--- a/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333D19FB-6929-46F0-85D3-422CA25B6010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C0322B-9813-4512-AFF9-10172CE2262A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
+    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="321">
   <si>
     <t>StepNo</t>
   </si>
@@ -996,6 +996,12 @@
   </si>
   <si>
     <t>Login password from environment configuration</t>
+  </si>
+  <si>
+    <t>Click Find record to open the patient search form</t>
+  </si>
+  <si>
+    <t>lnkTaskPanePatient</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2C8E55-67E3-4639-8044-17114017BF27}">
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -1537,13 +1543,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>319</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>320</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1551,19 +1560,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1571,16 +1574,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1588,13 +1594,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1602,19 +1611,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1622,13 +1625,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,13 +1645,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1650,19 +1659,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1670,19 +1673,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
       </c>
-      <c r="J16" t="s">
-        <v>34</v>
+      <c r="K16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1690,19 +1693,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
-      <c r="K17" t="s">
-        <v>52</v>
+      <c r="J17" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1710,19 +1713,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1730,16 +1733,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K19" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1747,13 +1753,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1761,13 +1770,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1775,19 +1784,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
       </c>
-      <c r="D22" t="s">
-        <v>62</v>
-      </c>
       <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1795,19 +1798,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
         <v>55</v>
       </c>
       <c r="K23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1815,19 +1818,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
       </c>
       <c r="K24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1835,16 +1838,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
         <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K25" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1852,13 +1858,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1866,16 +1875,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
-      <c r="D27" t="s">
-        <v>75</v>
-      </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1883,13 +1889,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1897,16 +1906,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
         <v>77</v>
       </c>
-      <c r="D29" t="s">
-        <v>79</v>
-      </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1914,13 +1920,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1928,19 +1937,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
         <v>81</v>
       </c>
-      <c r="D31" t="s">
-        <v>83</v>
-      </c>
       <c r="F31" t="s">
-        <v>84</v>
-      </c>
-      <c r="J31" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1948,7 +1951,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
         <v>81</v>
@@ -1957,13 +1960,10 @@
         <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="J32" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,16 +1971,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>87</v>
+      </c>
+      <c r="G33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1988,13 +1994,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2002,13 +2011,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2016,16 +2025,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,13 +2039,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>95</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2047,19 +2056,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
         <v>97</v>
       </c>
-      <c r="D38" t="s">
-        <v>32</v>
-      </c>
       <c r="F38" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2067,16 +2070,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
         <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="J39" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2084,13 +2090,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
         <v>97</v>
       </c>
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2098,16 +2107,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2115,13 +2121,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2129,25 +2138,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
         <v>105</v>
       </c>
-      <c r="D43" t="s">
-        <v>107</v>
-      </c>
       <c r="F43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" t="s">
-        <v>108</v>
-      </c>
-      <c r="H43" t="s">
-        <v>109</v>
-      </c>
-      <c r="J43" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2155,7 +2152,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
         <v>105</v>
@@ -2164,10 +2161,16 @@
         <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>84</v>
-      </c>
-      <c r="J44" t="s">
-        <v>111</v>
+        <v>87</v>
+      </c>
+      <c r="G44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H44" t="s">
+        <v>109</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2175,13 +2178,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>110</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>107</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="J45" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,16 +2198,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2206,13 +2212,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
         <v>105</v>
       </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2220,16 +2229,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C48" t="s">
         <v>105</v>
       </c>
-      <c r="D48" t="s">
-        <v>117</v>
-      </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2237,13 +2243,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>105</v>
+      </c>
+      <c r="D49" t="s">
+        <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2251,19 +2260,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
         <v>119</v>
       </c>
-      <c r="D50" t="s">
-        <v>121</v>
-      </c>
       <c r="F50" t="s">
-        <v>55</v>
-      </c>
-      <c r="K50" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2271,19 +2274,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
         <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F51" t="s">
         <v>55</v>
       </c>
       <c r="K51" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2291,19 +2294,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C52" t="s">
         <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F52" t="s">
         <v>55</v>
       </c>
       <c r="K52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2311,19 +2314,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
         <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F53" t="s">
         <v>55</v>
       </c>
       <c r="K53" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2331,16 +2334,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K54" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2348,13 +2354,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>119</v>
+      </c>
+      <c r="D55" t="s">
+        <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2362,16 +2371,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s">
         <v>135</v>
       </c>
-      <c r="D56" t="s">
-        <v>137</v>
-      </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2379,13 +2385,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>105</v>
+        <v>135</v>
+      </c>
+      <c r="D57" t="s">
+        <v>137</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2393,13 +2402,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
       </c>
       <c r="F58" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2407,16 +2416,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
-      </c>
-      <c r="C59" t="s">
-        <v>141</v>
-      </c>
-      <c r="D59" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2424,13 +2430,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
       </c>
+      <c r="D60" t="s">
+        <v>142</v>
+      </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2438,19 +2447,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
         <v>141</v>
       </c>
-      <c r="D61" t="s">
-        <v>145</v>
-      </c>
-      <c r="E61" t="s">
-        <v>146</v>
-      </c>
       <c r="F61" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2458,13 +2461,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>141</v>
+      </c>
+      <c r="D62" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" t="s">
+        <v>146</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2472,13 +2481,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
       </c>
       <c r="F63" t="s">
-        <v>22</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2486,16 +2495,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F64" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2503,13 +2509,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
+        <v>151</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2517,19 +2526,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
         <v>153</v>
       </c>
-      <c r="D66" t="s">
-        <v>155</v>
-      </c>
       <c r="F66" t="s">
-        <v>55</v>
-      </c>
-      <c r="K66" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2537,19 +2540,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
         <v>153</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F67" t="s">
         <v>55</v>
       </c>
       <c r="K67" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2557,19 +2560,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
         <v>153</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F68" t="s">
         <v>55</v>
       </c>
       <c r="K68" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2577,19 +2580,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C69" t="s">
         <v>153</v>
       </c>
       <c r="D69" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>55</v>
       </c>
       <c r="K69" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2597,19 +2600,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
         <v>153</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s">
         <v>55</v>
       </c>
       <c r="K70" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2617,16 +2620,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
         <v>153</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K71" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2634,13 +2640,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
         <v>153</v>
       </c>
+      <c r="D72" t="s">
+        <v>58</v>
+      </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2648,16 +2657,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
         <v>153</v>
       </c>
-      <c r="D73" t="s">
-        <v>133</v>
-      </c>
       <c r="F73" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2665,16 +2671,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>153</v>
+      </c>
+      <c r="D74" t="s">
+        <v>133</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2682,16 +2688,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
         <v>173</v>
       </c>
-      <c r="D75" t="s">
-        <v>137</v>
-      </c>
       <c r="F75" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,13 +2705,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>173</v>
+      </c>
+      <c r="D76" t="s">
+        <v>137</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2713,13 +2722,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="C77" t="s">
+        <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
-      </c>
-      <c r="J77">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2727,24 +2736,12 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" t="s">
-        <v>148</v>
-      </c>
-      <c r="D78" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>87</v>
-      </c>
-      <c r="G78" t="s">
-        <v>108</v>
-      </c>
-      <c r="H78" t="s">
-        <v>109</v>
-      </c>
-      <c r="J78" t="b">
+        <v>22</v>
+      </c>
+      <c r="J78">
         <v>1</v>
       </c>
     </row>
@@ -2753,12 +2750,24 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>177</v>
+      </c>
+      <c r="C79" t="s">
+        <v>148</v>
+      </c>
+      <c r="D79" t="s">
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>22</v>
-      </c>
-      <c r="J79">
+        <v>87</v>
+      </c>
+      <c r="G79" t="s">
+        <v>108</v>
+      </c>
+      <c r="H79" t="s">
+        <v>109</v>
+      </c>
+      <c r="J79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2767,16 +2776,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" t="s">
-        <v>148</v>
-      </c>
-      <c r="D80" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2784,13 +2790,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
         <v>148</v>
       </c>
+      <c r="D81" t="s">
+        <v>181</v>
+      </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2798,16 +2807,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C82" t="s">
         <v>148</v>
       </c>
-      <c r="D82" t="s">
-        <v>184</v>
-      </c>
       <c r="F82" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2815,13 +2821,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2829,19 +2838,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C84" t="s">
         <v>186</v>
       </c>
-      <c r="D84" t="s">
-        <v>155</v>
-      </c>
       <c r="F84" t="s">
-        <v>55</v>
-      </c>
-      <c r="K84" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2849,19 +2852,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C85" t="s">
         <v>186</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F85" t="s">
         <v>55</v>
       </c>
       <c r="K85" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2869,19 +2872,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C86" t="s">
         <v>186</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F86" t="s">
         <v>55</v>
       </c>
       <c r="K86" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2889,19 +2892,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C87" t="s">
         <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F87" t="s">
         <v>55</v>
       </c>
       <c r="K87" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,19 +2912,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F88" t="s">
         <v>55</v>
       </c>
       <c r="K88" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2929,19 +2932,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C89" t="s">
         <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="F89" t="s">
         <v>55</v>
       </c>
       <c r="K89" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2949,16 +2952,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
         <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K90" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2966,13 +2972,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C91" t="s">
         <v>186</v>
       </c>
+      <c r="D91" t="s">
+        <v>58</v>
+      </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2980,16 +2989,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C92" t="s">
         <v>186</v>
       </c>
-      <c r="D92" t="s">
-        <v>133</v>
-      </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -2997,13 +3003,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C93" t="s">
-        <v>199</v>
+        <v>186</v>
+      </c>
+      <c r="D93" t="s">
+        <v>133</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3011,16 +3020,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C94" t="s">
         <v>199</v>
       </c>
-      <c r="D94" t="s">
-        <v>201</v>
-      </c>
       <c r="F94" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3028,13 +3034,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>199</v>
+      </c>
+      <c r="D95" t="s">
+        <v>201</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3042,13 +3051,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="C96" t="s">
+        <v>148</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
-      </c>
-      <c r="J96">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3056,24 +3065,12 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>204</v>
-      </c>
-      <c r="C97" t="s">
-        <v>148</v>
-      </c>
-      <c r="D97" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s">
-        <v>87</v>
-      </c>
-      <c r="G97" t="s">
-        <v>108</v>
-      </c>
-      <c r="H97" t="s">
-        <v>109</v>
-      </c>
-      <c r="J97" t="b">
+        <v>22</v>
+      </c>
+      <c r="J97">
         <v>1</v>
       </c>
     </row>
@@ -3082,12 +3079,24 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>205</v>
+        <v>204</v>
+      </c>
+      <c r="C98" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" t="s">
+        <v>178</v>
       </c>
       <c r="F98" t="s">
-        <v>22</v>
-      </c>
-      <c r="J98">
+        <v>87</v>
+      </c>
+      <c r="G98" t="s">
+        <v>108</v>
+      </c>
+      <c r="H98" t="s">
+        <v>109</v>
+      </c>
+      <c r="J98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3096,16 +3105,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
-      </c>
-      <c r="C99" t="s">
-        <v>148</v>
-      </c>
-      <c r="D99" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3113,13 +3119,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C100" t="s">
         <v>148</v>
       </c>
+      <c r="D100" t="s">
+        <v>181</v>
+      </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -3127,16 +3136,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C101" t="s">
         <v>148</v>
       </c>
-      <c r="D101" t="s">
-        <v>209</v>
-      </c>
       <c r="F101" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3144,13 +3150,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C102" t="s">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="D102" t="s">
+        <v>209</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -3158,19 +3167,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C103" t="s">
         <v>186</v>
       </c>
-      <c r="D103" t="s">
-        <v>155</v>
-      </c>
       <c r="F103" t="s">
-        <v>55</v>
-      </c>
-      <c r="K103" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -3178,19 +3181,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C104" t="s">
         <v>186</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F104" t="s">
         <v>55</v>
       </c>
       <c r="K104" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -3198,19 +3201,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C105" t="s">
         <v>186</v>
       </c>
       <c r="D105" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F105" t="s">
         <v>55</v>
       </c>
       <c r="K105" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3218,19 +3221,19 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C106" t="s">
         <v>186</v>
       </c>
       <c r="D106" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F106" t="s">
         <v>55</v>
       </c>
       <c r="K106" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3238,19 +3241,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
         <v>186</v>
       </c>
       <c r="D107" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F107" t="s">
         <v>55</v>
       </c>
       <c r="K107" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -3258,19 +3261,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C108" t="s">
         <v>186</v>
       </c>
       <c r="D108" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="F108" t="s">
         <v>55</v>
       </c>
       <c r="K108" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -3278,16 +3281,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C109" t="s">
         <v>186</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K109" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -3295,13 +3301,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C110" t="s">
         <v>186</v>
       </c>
+      <c r="D110" t="s">
+        <v>58</v>
+      </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -3309,16 +3318,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C111" t="s">
         <v>186</v>
       </c>
-      <c r="D111" t="s">
-        <v>133</v>
-      </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -3326,13 +3332,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
-        <v>199</v>
+        <v>186</v>
+      </c>
+      <c r="D112" t="s">
+        <v>133</v>
       </c>
       <c r="F112" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -3340,16 +3349,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C113" t="s">
         <v>199</v>
       </c>
-      <c r="D113" t="s">
-        <v>201</v>
-      </c>
       <c r="F113" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -3357,13 +3363,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>199</v>
+      </c>
+      <c r="D114" t="s">
+        <v>201</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -3371,13 +3380,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>222</v>
+      </c>
+      <c r="C115" t="s">
+        <v>148</v>
       </c>
       <c r="F115" t="s">
-        <v>22</v>
-      </c>
-      <c r="J115">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -3385,24 +3394,12 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>224</v>
-      </c>
-      <c r="C116" t="s">
-        <v>148</v>
-      </c>
-      <c r="D116" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="F116" t="s">
-        <v>87</v>
-      </c>
-      <c r="G116" t="s">
-        <v>108</v>
-      </c>
-      <c r="H116" t="s">
-        <v>109</v>
-      </c>
-      <c r="J116" t="b">
+        <v>22</v>
+      </c>
+      <c r="J116">
         <v>1</v>
       </c>
     </row>
@@ -3411,12 +3408,24 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>224</v>
+      </c>
+      <c r="C117" t="s">
+        <v>148</v>
+      </c>
+      <c r="D117" t="s">
+        <v>178</v>
       </c>
       <c r="F117" t="s">
-        <v>22</v>
-      </c>
-      <c r="J117">
+        <v>87</v>
+      </c>
+      <c r="G117" t="s">
+        <v>108</v>
+      </c>
+      <c r="H117" t="s">
+        <v>109</v>
+      </c>
+      <c r="J117" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3425,16 +3434,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
-      </c>
-      <c r="C118" t="s">
-        <v>148</v>
-      </c>
-      <c r="D118" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -3442,13 +3448,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
         <v>148</v>
       </c>
+      <c r="D119" t="s">
+        <v>25</v>
+      </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -3456,16 +3465,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C120" t="s">
         <v>148</v>
       </c>
-      <c r="D120" t="s">
-        <v>25</v>
-      </c>
       <c r="F120" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -3473,13 +3479,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
         <v>148</v>
       </c>
+      <c r="D121" t="s">
+        <v>25</v>
+      </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -3487,25 +3496,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C122" t="s">
         <v>148</v>
       </c>
-      <c r="D122" t="s">
-        <v>87</v>
-      </c>
       <c r="F122" t="s">
-        <v>87</v>
-      </c>
-      <c r="G122" t="s">
-        <v>108</v>
-      </c>
-      <c r="H122" t="s">
-        <v>109</v>
-      </c>
-      <c r="J122" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -3513,12 +3510,24 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="C123" t="s">
+        <v>148</v>
+      </c>
+      <c r="D123" t="s">
+        <v>87</v>
       </c>
       <c r="F123" t="s">
-        <v>22</v>
-      </c>
-      <c r="J123">
+        <v>87</v>
+      </c>
+      <c r="G123" t="s">
+        <v>108</v>
+      </c>
+      <c r="H123" t="s">
+        <v>109</v>
+      </c>
+      <c r="J123" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3527,24 +3536,12 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>232</v>
-      </c>
-      <c r="C124" t="s">
-        <v>148</v>
-      </c>
-      <c r="D124" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="F124" t="s">
-        <v>87</v>
-      </c>
-      <c r="G124" t="s">
-        <v>108</v>
-      </c>
-      <c r="H124" t="s">
-        <v>109</v>
-      </c>
-      <c r="J124" t="b">
+        <v>22</v>
+      </c>
+      <c r="J124">
         <v>1</v>
       </c>
     </row>
@@ -3553,12 +3550,24 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>233</v>
+        <v>232</v>
+      </c>
+      <c r="C125" t="s">
+        <v>148</v>
+      </c>
+      <c r="D125" t="s">
+        <v>178</v>
       </c>
       <c r="F125" t="s">
-        <v>22</v>
-      </c>
-      <c r="J125">
+        <v>87</v>
+      </c>
+      <c r="G125" t="s">
+        <v>108</v>
+      </c>
+      <c r="H125" t="s">
+        <v>109</v>
+      </c>
+      <c r="J125" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3567,16 +3576,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>234</v>
-      </c>
-      <c r="C126" t="s">
-        <v>148</v>
-      </c>
-      <c r="D126" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="F126" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,13 +3590,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C127" t="s">
         <v>148</v>
       </c>
       <c r="D127" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="F127" t="s">
         <v>25</v>
@@ -3601,13 +3607,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
-        <v>238</v>
+        <v>148</v>
+      </c>
+      <c r="D128" t="s">
+        <v>236</v>
       </c>
       <c r="F128" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -3615,19 +3624,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C129" t="s">
         <v>238</v>
       </c>
-      <c r="D129" t="s">
-        <v>155</v>
-      </c>
       <c r="F129" t="s">
-        <v>55</v>
-      </c>
-      <c r="K129" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -3635,19 +3638,19 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C130" t="s">
         <v>238</v>
       </c>
       <c r="D130" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F130" t="s">
         <v>55</v>
       </c>
       <c r="K130" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3655,19 +3658,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s">
         <v>238</v>
       </c>
       <c r="D131" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F131" t="s">
         <v>55</v>
       </c>
       <c r="K131" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -3675,16 +3678,19 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C132" t="s">
         <v>238</v>
       </c>
       <c r="D132" t="s">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="F132" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K132" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -3692,13 +3698,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C133" t="s">
         <v>238</v>
       </c>
+      <c r="D133" t="s">
+        <v>243</v>
+      </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -3706,16 +3715,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C134" t="s">
         <v>238</v>
       </c>
-      <c r="D134" t="s">
-        <v>246</v>
-      </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -3723,13 +3729,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C135" t="s">
         <v>238</v>
       </c>
+      <c r="D135" t="s">
+        <v>246</v>
+      </c>
       <c r="F135" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -3737,19 +3746,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C136" t="s">
         <v>238</v>
       </c>
-      <c r="D136" t="s">
-        <v>193</v>
-      </c>
       <c r="F136" t="s">
-        <v>55</v>
-      </c>
-      <c r="K136" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -3757,16 +3760,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C137" t="s">
         <v>238</v>
       </c>
       <c r="D137" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="K137" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -3774,13 +3780,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C138" t="s">
-        <v>148</v>
+        <v>238</v>
+      </c>
+      <c r="D138" t="s">
+        <v>133</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -3788,13 +3797,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>251</v>
+        <v>250</v>
+      </c>
+      <c r="C139" t="s">
+        <v>148</v>
       </c>
       <c r="F139" t="s">
-        <v>22</v>
-      </c>
-      <c r="J139">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -3802,24 +3811,12 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>252</v>
-      </c>
-      <c r="C140" t="s">
-        <v>148</v>
-      </c>
-      <c r="D140" t="s">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="F140" t="s">
-        <v>87</v>
-      </c>
-      <c r="G140" t="s">
-        <v>108</v>
-      </c>
-      <c r="H140" t="s">
-        <v>109</v>
-      </c>
-      <c r="J140" t="b">
+        <v>22</v>
+      </c>
+      <c r="J140">
         <v>1</v>
       </c>
     </row>
@@ -3828,12 +3825,24 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>253</v>
+        <v>252</v>
+      </c>
+      <c r="C141" t="s">
+        <v>148</v>
+      </c>
+      <c r="D141" t="s">
+        <v>178</v>
       </c>
       <c r="F141" t="s">
-        <v>22</v>
-      </c>
-      <c r="J141">
+        <v>87</v>
+      </c>
+      <c r="G141" t="s">
+        <v>108</v>
+      </c>
+      <c r="H141" t="s">
+        <v>109</v>
+      </c>
+      <c r="J141" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3842,16 +3851,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>254</v>
-      </c>
-      <c r="C142" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F142" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -3859,15 +3865,32 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C143" t="s">
         <v>19</v>
       </c>
       <c r="D143" t="s">
+        <v>255</v>
+      </c>
+      <c r="F143" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>256</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" t="s">
         <v>257</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F144" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4257,4 +4280,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C0322B-9813-4512-AFF9-10172CE2262A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB992F2-FE2E-46CF-B5EE-0D550E3FB6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="320">
   <si>
     <t>StepNo</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>Click Find to search for patients with the generated surname</t>
-  </si>
-  <si>
-    <t>pageRoadMapButtons</t>
   </si>
   <si>
     <t>btn_Find</t>
@@ -1543,13 +1540,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -1597,10 +1594,10 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -1611,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -1625,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -1645,10 +1642,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
         <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
@@ -1659,7 +1656,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
@@ -1673,19 +1670,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1693,10 +1690,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -1713,19 +1710,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
         <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
       </c>
       <c r="K18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,19 +1730,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>54</v>
       </c>
-      <c r="F19" t="s">
+      <c r="K19" t="s">
         <v>55</v>
-      </c>
-      <c r="K19" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1753,13 +1750,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>58</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -1770,7 +1767,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
@@ -1784,10 +1781,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s">
         <v>20</v>
@@ -1798,19 +1795,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K23" t="s">
         <v>62</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1818,19 +1815,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" t="s">
         <v>65</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K24" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1838,19 +1835,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" t="s">
         <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="K25" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1858,13 +1855,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
         <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -1875,10 +1872,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
         <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1889,13 +1886,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" t="s">
         <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -1906,10 +1903,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
         <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1920,13 +1917,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>79</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -1937,10 +1934,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
         <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1951,19 +1948,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
         <v>82</v>
       </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>83</v>
       </c>
-      <c r="F32" t="s">
+      <c r="J32" t="s">
         <v>84</v>
-      </c>
-      <c r="J32" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,22 +1968,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" t="s">
         <v>86</v>
       </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>87</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>88</v>
-      </c>
-      <c r="H33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1994,13 +1991,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
         <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>91</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -2011,7 +2008,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
@@ -2025,7 +2022,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
         <v>22</v>
@@ -2039,13 +2036,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -2056,10 +2053,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" t="s">
         <v>96</v>
-      </c>
-      <c r="C38" t="s">
-        <v>97</v>
       </c>
       <c r="F38" t="s">
         <v>20</v>
@@ -2070,10 +2067,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
         <v>32</v>
@@ -2090,13 +2087,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -2107,10 +2104,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -2121,13 +2118,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" t="s">
         <v>101</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>102</v>
-      </c>
-      <c r="D42" t="s">
-        <v>103</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -2138,10 +2135,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" t="s">
         <v>104</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
@@ -2152,22 +2149,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" t="s">
         <v>106</v>
       </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
+        <v>86</v>
+      </c>
+      <c r="G44" t="s">
         <v>107</v>
       </c>
-      <c r="F44" t="s">
-        <v>87</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>108</v>
-      </c>
-      <c r="H44" t="s">
-        <v>109</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
@@ -2178,19 +2175,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45" t="s">
         <v>110</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>107</v>
-      </c>
-      <c r="F45" t="s">
-        <v>84</v>
-      </c>
-      <c r="J45" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2198,7 +2195,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F46" t="s">
         <v>22</v>
@@ -2212,13 +2209,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" t="s">
         <v>113</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" t="s">
-        <v>114</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -2229,10 +2226,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F48" t="s">
         <v>20</v>
@@ -2243,13 +2240,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
         <v>116</v>
-      </c>
-      <c r="C49" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" t="s">
-        <v>117</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -2260,10 +2257,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" t="s">
         <v>118</v>
-      </c>
-      <c r="C50" t="s">
-        <v>119</v>
       </c>
       <c r="F50" t="s">
         <v>20</v>
@@ -2274,19 +2271,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" t="s">
         <v>120</v>
       </c>
-      <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K51" t="s">
         <v>121</v>
-      </c>
-      <c r="F51" t="s">
-        <v>55</v>
-      </c>
-      <c r="K51" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2294,19 +2291,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
         <v>123</v>
       </c>
-      <c r="C52" t="s">
-        <v>119</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>54</v>
+      </c>
+      <c r="K52" t="s">
         <v>124</v>
-      </c>
-      <c r="F52" t="s">
-        <v>55</v>
-      </c>
-      <c r="K52" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2314,19 +2311,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" t="s">
         <v>126</v>
       </c>
-      <c r="C53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="K53" t="s">
         <v>127</v>
-      </c>
-      <c r="F53" t="s">
-        <v>55</v>
-      </c>
-      <c r="K53" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2334,19 +2331,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" t="s">
         <v>129</v>
       </c>
-      <c r="C54" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>54</v>
+      </c>
+      <c r="K54" t="s">
         <v>130</v>
-      </c>
-      <c r="F54" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2354,13 +2351,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" t="s">
         <v>132</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>133</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -2371,10 +2368,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" t="s">
         <v>134</v>
-      </c>
-      <c r="C56" t="s">
-        <v>135</v>
       </c>
       <c r="F56" t="s">
         <v>20</v>
@@ -2385,13 +2382,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" t="s">
         <v>136</v>
-      </c>
-      <c r="C57" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" t="s">
-        <v>137</v>
       </c>
       <c r="F57" t="s">
         <v>25</v>
@@ -2402,10 +2399,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F58" t="s">
         <v>20</v>
@@ -2416,7 +2413,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
@@ -2430,13 +2427,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" t="s">
         <v>140</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>141</v>
-      </c>
-      <c r="D60" t="s">
-        <v>142</v>
       </c>
       <c r="F60" t="s">
         <v>25</v>
@@ -2447,10 +2444,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F61" t="s">
         <v>20</v>
@@ -2461,16 +2458,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" t="s">
         <v>144</v>
       </c>
-      <c r="C62" t="s">
-        <v>141</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>145</v>
-      </c>
-      <c r="E62" t="s">
-        <v>146</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
@@ -2481,10 +2478,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" t="s">
         <v>147</v>
-      </c>
-      <c r="C63" t="s">
-        <v>148</v>
       </c>
       <c r="F63" t="s">
         <v>20</v>
@@ -2495,7 +2492,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>22</v>
@@ -2509,13 +2506,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s">
+        <v>147</v>
+      </c>
+      <c r="D65" t="s">
         <v>150</v>
-      </c>
-      <c r="C65" t="s">
-        <v>148</v>
-      </c>
-      <c r="D65" t="s">
-        <v>151</v>
       </c>
       <c r="F65" t="s">
         <v>25</v>
@@ -2526,10 +2523,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" t="s">
         <v>152</v>
-      </c>
-      <c r="C66" t="s">
-        <v>153</v>
       </c>
       <c r="F66" t="s">
         <v>20</v>
@@ -2540,19 +2537,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>152</v>
+      </c>
+      <c r="D67" t="s">
         <v>154</v>
       </c>
-      <c r="C67" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="F67" t="s">
+        <v>54</v>
+      </c>
+      <c r="K67" t="s">
         <v>155</v>
-      </c>
-      <c r="F67" t="s">
-        <v>55</v>
-      </c>
-      <c r="K67" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2560,19 +2557,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" t="s">
         <v>157</v>
       </c>
-      <c r="C68" t="s">
-        <v>153</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
+        <v>54</v>
+      </c>
+      <c r="K68" t="s">
         <v>158</v>
-      </c>
-      <c r="F68" t="s">
-        <v>55</v>
-      </c>
-      <c r="K68" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2580,19 +2577,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" t="s">
         <v>160</v>
       </c>
-      <c r="C69" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
+        <v>54</v>
+      </c>
+      <c r="K69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>55</v>
-      </c>
-      <c r="K69" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2600,19 +2597,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" t="s">
+        <v>152</v>
+      </c>
+      <c r="D70" t="s">
         <v>163</v>
       </c>
-      <c r="C70" t="s">
-        <v>153</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
+        <v>54</v>
+      </c>
+      <c r="K70" t="s">
         <v>164</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-      <c r="K70" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2620,19 +2617,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" t="s">
+        <v>152</v>
+      </c>
+      <c r="D71" t="s">
         <v>166</v>
       </c>
-      <c r="C71" t="s">
-        <v>153</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
+        <v>54</v>
+      </c>
+      <c r="K71" t="s">
         <v>167</v>
-      </c>
-      <c r="F71" t="s">
-        <v>55</v>
-      </c>
-      <c r="K71" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2640,13 +2637,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" t="s">
         <v>25</v>
@@ -2657,10 +2654,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F73" t="s">
         <v>20</v>
@@ -2671,13 +2668,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F74" t="s">
         <v>25</v>
@@ -2688,10 +2685,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" t="s">
         <v>172</v>
-      </c>
-      <c r="C75" t="s">
-        <v>173</v>
       </c>
       <c r="F75" t="s">
         <v>22</v>
@@ -2705,13 +2702,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F76" t="s">
         <v>25</v>
@@ -2722,10 +2719,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F77" t="s">
         <v>20</v>
@@ -2736,7 +2733,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>22</v>
@@ -2750,22 +2747,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" t="s">
+        <v>147</v>
+      </c>
+      <c r="D79" t="s">
         <v>177</v>
       </c>
-      <c r="C79" t="s">
-        <v>148</v>
-      </c>
-      <c r="D79" t="s">
-        <v>178</v>
-      </c>
       <c r="F79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G79" t="s">
+        <v>107</v>
+      </c>
+      <c r="H79" t="s">
         <v>108</v>
-      </c>
-      <c r="H79" t="s">
-        <v>109</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
@@ -2776,7 +2773,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F80" t="s">
         <v>22</v>
@@ -2790,13 +2787,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" t="s">
+        <v>147</v>
+      </c>
+      <c r="D81" t="s">
         <v>180</v>
-      </c>
-      <c r="C81" t="s">
-        <v>148</v>
-      </c>
-      <c r="D81" t="s">
-        <v>181</v>
       </c>
       <c r="F81" t="s">
         <v>25</v>
@@ -2807,10 +2804,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F82" t="s">
         <v>20</v>
@@ -2821,13 +2818,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>147</v>
+      </c>
+      <c r="D83" t="s">
         <v>183</v>
-      </c>
-      <c r="C83" t="s">
-        <v>148</v>
-      </c>
-      <c r="D83" t="s">
-        <v>184</v>
       </c>
       <c r="F83" t="s">
         <v>25</v>
@@ -2838,10 +2835,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
         <v>185</v>
-      </c>
-      <c r="C84" t="s">
-        <v>186</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -2852,19 +2849,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D85" t="s">
+        <v>154</v>
+      </c>
+      <c r="F85" t="s">
+        <v>54</v>
+      </c>
+      <c r="K85" t="s">
         <v>155</v>
-      </c>
-      <c r="F85" t="s">
-        <v>55</v>
-      </c>
-      <c r="K85" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2872,19 +2869,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D86" t="s">
+        <v>157</v>
+      </c>
+      <c r="F86" t="s">
+        <v>54</v>
+      </c>
+      <c r="K86" t="s">
         <v>158</v>
-      </c>
-      <c r="F86" t="s">
-        <v>55</v>
-      </c>
-      <c r="K86" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2892,19 +2889,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D87" t="s">
+        <v>160</v>
+      </c>
+      <c r="F87" t="s">
+        <v>54</v>
+      </c>
+      <c r="K87" t="s">
         <v>161</v>
-      </c>
-      <c r="F87" t="s">
-        <v>55</v>
-      </c>
-      <c r="K87" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2912,19 +2909,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D88" t="s">
+        <v>163</v>
+      </c>
+      <c r="F88" t="s">
+        <v>54</v>
+      </c>
+      <c r="K88" t="s">
         <v>164</v>
-      </c>
-      <c r="F88" t="s">
-        <v>55</v>
-      </c>
-      <c r="K88" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2932,19 +2929,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D89" t="s">
+        <v>166</v>
+      </c>
+      <c r="F89" t="s">
+        <v>54</v>
+      </c>
+      <c r="K89" t="s">
         <v>167</v>
-      </c>
-      <c r="F89" t="s">
-        <v>55</v>
-      </c>
-      <c r="K89" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2952,19 +2949,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" t="s">
+        <v>185</v>
+      </c>
+      <c r="D90" t="s">
         <v>192</v>
       </c>
-      <c r="C90" t="s">
-        <v>186</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
+        <v>54</v>
+      </c>
+      <c r="K90" t="s">
         <v>193</v>
-      </c>
-      <c r="F90" t="s">
-        <v>55</v>
-      </c>
-      <c r="K90" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2972,13 +2969,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
@@ -2989,10 +2986,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F92" t="s">
         <v>20</v>
@@ -3003,13 +3000,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
@@ -3020,10 +3017,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" t="s">
         <v>198</v>
-      </c>
-      <c r="C94" t="s">
-        <v>199</v>
       </c>
       <c r="F94" t="s">
         <v>20</v>
@@ -3034,13 +3031,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>199</v>
+      </c>
+      <c r="C95" t="s">
+        <v>198</v>
+      </c>
+      <c r="D95" t="s">
         <v>200</v>
-      </c>
-      <c r="C95" t="s">
-        <v>199</v>
-      </c>
-      <c r="D95" t="s">
-        <v>201</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
@@ -3051,10 +3048,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F96" t="s">
         <v>20</v>
@@ -3065,7 +3062,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F97" t="s">
         <v>22</v>
@@ -3079,22 +3076,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F98" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G98" t="s">
+        <v>107</v>
+      </c>
+      <c r="H98" t="s">
         <v>108</v>
-      </c>
-      <c r="H98" t="s">
-        <v>109</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
@@ -3105,7 +3102,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F99" t="s">
         <v>22</v>
@@ -3119,13 +3116,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D100" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -3136,10 +3133,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -3150,13 +3147,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>207</v>
+      </c>
+      <c r="C102" t="s">
+        <v>147</v>
+      </c>
+      <c r="D102" t="s">
         <v>208</v>
-      </c>
-      <c r="C102" t="s">
-        <v>148</v>
-      </c>
-      <c r="D102" t="s">
-        <v>209</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -3167,10 +3164,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
@@ -3181,19 +3178,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C104" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D104" t="s">
+        <v>154</v>
+      </c>
+      <c r="F104" t="s">
+        <v>54</v>
+      </c>
+      <c r="K104" t="s">
         <v>155</v>
-      </c>
-      <c r="F104" t="s">
-        <v>55</v>
-      </c>
-      <c r="K104" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -3201,19 +3198,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D105" t="s">
+        <v>157</v>
+      </c>
+      <c r="F105" t="s">
+        <v>54</v>
+      </c>
+      <c r="K105" t="s">
         <v>158</v>
-      </c>
-      <c r="F105" t="s">
-        <v>55</v>
-      </c>
-      <c r="K105" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3221,19 +3218,19 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C106" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D106" t="s">
+        <v>160</v>
+      </c>
+      <c r="F106" t="s">
+        <v>54</v>
+      </c>
+      <c r="K106" t="s">
         <v>161</v>
-      </c>
-      <c r="F106" t="s">
-        <v>55</v>
-      </c>
-      <c r="K106" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3241,19 +3238,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D107" t="s">
+        <v>163</v>
+      </c>
+      <c r="F107" t="s">
+        <v>54</v>
+      </c>
+      <c r="K107" t="s">
         <v>164</v>
-      </c>
-      <c r="F107" t="s">
-        <v>55</v>
-      </c>
-      <c r="K107" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -3261,19 +3258,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D108" t="s">
+        <v>166</v>
+      </c>
+      <c r="F108" t="s">
+        <v>54</v>
+      </c>
+      <c r="K108" t="s">
         <v>167</v>
-      </c>
-      <c r="F108" t="s">
-        <v>55</v>
-      </c>
-      <c r="K108" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -3281,19 +3278,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D109" t="s">
+        <v>192</v>
+      </c>
+      <c r="F109" t="s">
+        <v>54</v>
+      </c>
+      <c r="K109" t="s">
         <v>193</v>
-      </c>
-      <c r="F109" t="s">
-        <v>55</v>
-      </c>
-      <c r="K109" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -3301,13 +3298,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D110" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F110" t="s">
         <v>25</v>
@@ -3318,10 +3315,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F111" t="s">
         <v>20</v>
@@ -3332,13 +3329,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D112" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F112" t="s">
         <v>25</v>
@@ -3349,10 +3346,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F113" t="s">
         <v>20</v>
@@ -3363,13 +3360,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D114" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F114" t="s">
         <v>25</v>
@@ -3380,10 +3377,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F115" t="s">
         <v>20</v>
@@ -3394,7 +3391,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F116" t="s">
         <v>22</v>
@@ -3408,22 +3405,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F117" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G117" t="s">
+        <v>107</v>
+      </c>
+      <c r="H117" t="s">
         <v>108</v>
-      </c>
-      <c r="H117" t="s">
-        <v>109</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
@@ -3434,7 +3431,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F118" t="s">
         <v>22</v>
@@ -3448,10 +3445,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C119" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D119" t="s">
         <v>25</v>
@@ -3465,10 +3462,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C120" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -3479,10 +3476,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C121" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D121" t="s">
         <v>25</v>
@@ -3496,10 +3493,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C122" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F122" t="s">
         <v>20</v>
@@ -3510,22 +3507,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C123" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D123" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F123" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G123" t="s">
+        <v>107</v>
+      </c>
+      <c r="H123" t="s">
         <v>108</v>
-      </c>
-      <c r="H123" t="s">
-        <v>109</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
@@ -3536,7 +3533,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
@@ -3550,22 +3547,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C125" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D125" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F125" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G125" t="s">
+        <v>107</v>
+      </c>
+      <c r="H125" t="s">
         <v>108</v>
-      </c>
-      <c r="H125" t="s">
-        <v>109</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
@@ -3576,7 +3573,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -3590,13 +3587,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C127" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D127" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F127" t="s">
         <v>25</v>
@@ -3607,13 +3604,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>234</v>
+      </c>
+      <c r="C128" t="s">
+        <v>147</v>
+      </c>
+      <c r="D128" t="s">
         <v>235</v>
-      </c>
-      <c r="C128" t="s">
-        <v>148</v>
-      </c>
-      <c r="D128" t="s">
-        <v>236</v>
       </c>
       <c r="F128" t="s">
         <v>25</v>
@@ -3624,10 +3621,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>236</v>
+      </c>
+      <c r="C129" t="s">
         <v>237</v>
-      </c>
-      <c r="C129" t="s">
-        <v>238</v>
       </c>
       <c r="F129" t="s">
         <v>20</v>
@@ -3638,19 +3635,19 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C130" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D130" t="s">
+        <v>154</v>
+      </c>
+      <c r="F130" t="s">
+        <v>54</v>
+      </c>
+      <c r="K130" t="s">
         <v>155</v>
-      </c>
-      <c r="F130" t="s">
-        <v>55</v>
-      </c>
-      <c r="K130" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3658,19 +3655,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C131" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D131" t="s">
+        <v>157</v>
+      </c>
+      <c r="F131" t="s">
+        <v>54</v>
+      </c>
+      <c r="K131" t="s">
         <v>158</v>
-      </c>
-      <c r="F131" t="s">
-        <v>55</v>
-      </c>
-      <c r="K131" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -3678,19 +3675,19 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D132" t="s">
+        <v>166</v>
+      </c>
+      <c r="F132" t="s">
+        <v>54</v>
+      </c>
+      <c r="K132" t="s">
         <v>167</v>
-      </c>
-      <c r="F132" t="s">
-        <v>55</v>
-      </c>
-      <c r="K132" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -3698,13 +3695,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>241</v>
+      </c>
+      <c r="C133" t="s">
+        <v>237</v>
+      </c>
+      <c r="D133" t="s">
         <v>242</v>
-      </c>
-      <c r="C133" t="s">
-        <v>238</v>
-      </c>
-      <c r="D133" t="s">
-        <v>243</v>
       </c>
       <c r="F133" t="s">
         <v>25</v>
@@ -3715,10 +3712,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C134" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F134" t="s">
         <v>20</v>
@@ -3729,13 +3726,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>244</v>
+      </c>
+      <c r="C135" t="s">
+        <v>237</v>
+      </c>
+      <c r="D135" t="s">
         <v>245</v>
-      </c>
-      <c r="C135" t="s">
-        <v>238</v>
-      </c>
-      <c r="D135" t="s">
-        <v>246</v>
       </c>
       <c r="F135" t="s">
         <v>25</v>
@@ -3746,10 +3743,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C136" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F136" t="s">
         <v>20</v>
@@ -3760,19 +3757,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C137" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D137" t="s">
+        <v>192</v>
+      </c>
+      <c r="F137" t="s">
+        <v>54</v>
+      </c>
+      <c r="K137" t="s">
         <v>193</v>
-      </c>
-      <c r="F137" t="s">
-        <v>55</v>
-      </c>
-      <c r="K137" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -3780,13 +3777,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C138" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D138" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F138" t="s">
         <v>25</v>
@@ -3797,10 +3794,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C139" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F139" t="s">
         <v>20</v>
@@ -3811,7 +3808,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F140" t="s">
         <v>22</v>
@@ -3825,22 +3822,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C141" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F141" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G141" t="s">
+        <v>107</v>
+      </c>
+      <c r="H141" t="s">
         <v>108</v>
-      </c>
-      <c r="H141" t="s">
-        <v>109</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
@@ -3851,7 +3848,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F142" t="s">
         <v>22</v>
@@ -3865,13 +3862,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C143" t="s">
         <v>19</v>
       </c>
       <c r="D143" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F143" t="s">
         <v>25</v>
@@ -3882,13 +3879,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C144" t="s">
         <v>19</v>
       </c>
       <c r="D144" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F144" t="s">
         <v>25</v>
@@ -3924,102 +3921,102 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" t="s">
         <v>258</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>259</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" t="s">
         <v>260</v>
       </c>
-      <c r="D2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>261</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>262</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>263</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>264</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>265</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>266</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>267</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>268</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>269</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>270</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>271</v>
-      </c>
-      <c r="P2" t="s">
-        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4038,71 +4035,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B9" s="3">
         <v>142</v>
@@ -4110,7 +4107,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B10" s="3">
         <v>21</v>
@@ -4118,7 +4115,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3">
         <v>52</v>
@@ -4126,15 +4123,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -4142,7 +4139,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -4150,31 +4147,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>299</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B18" s="3">
         <v>8</v>
@@ -4182,18 +4179,18 @@
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>302</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4213,13 +4210,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4227,54 +4224,54 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" t="s">
         <v>309</v>
-      </c>
-      <c r="C2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" t="s">
         <v>311</v>
-      </c>
-      <c r="C3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" t="s">
         <v>314</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>315</v>
-      </c>
-      <c r="C5" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6" t="s">
         <v>317</v>
       </c>
-      <c r="B6" t="s">
-        <v>318</v>
-      </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB992F2-FE2E-46CF-B5EE-0D550E3FB6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F619008C-7E7F-4849-AEE5-4BB39C0E1995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="332">
   <si>
     <t>StepNo</t>
   </si>
@@ -80,9 +80,6 @@
     <t>launchUrl</t>
   </si>
   <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
-  </si>
-  <si>
     <t>Login with valid credentials</t>
   </si>
   <si>
@@ -131,12 +128,6 @@
     <t>surname||_RandomSurname</t>
   </si>
   <si>
-    <t>Enter generated surname in the patient search form to confirm no existing record</t>
-  </si>
-  <si>
-    <t>pageSearchPatient</t>
-  </si>
-  <si>
     <t>txt_Surname</t>
   </si>
   <si>
@@ -146,859 +137,904 @@
     <t>_RandomSurname</t>
   </si>
   <si>
-    <t>Click Find to search for patients with the generated surname</t>
-  </si>
-  <si>
     <t>btn_Find</t>
   </si>
   <si>
-    <t>Wait for patient search results to confirm no existing record</t>
-  </si>
-  <si>
-    <t>Click Registration to initiate new patient registration roadmap from search results</t>
-  </si>
-  <si>
-    <t>pagePatientSearchResult</t>
-  </si>
-  <si>
-    <t>lnkTaskPaneViewEPR</t>
-  </si>
-  <si>
-    <t>Registration</t>
-  </si>
-  <si>
-    <t>Wait for patient registration roadmap form to load</t>
-  </si>
-  <si>
     <t>pageRegRegistration</t>
   </si>
   <si>
-    <t>-- PATIENT REGISTRATION ROADMAP - SECTION 1: PERSON DETAILS --</t>
-  </si>
-  <si>
-    <t>Enter patient forename in the registration form</t>
+    <t>FORENAME</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>cmb_Country</t>
+  </si>
+  <si>
+    <t>selectComboBox</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Click Next to proceed to the second section of the registration roadmap</t>
+  </si>
+  <si>
+    <t>btn_Next</t>
+  </si>
+  <si>
+    <t>-- PATIENT REGISTRATION ROADMAP - SECTION 2: ADDITIONAL DEMOGRAPHICS --</t>
+  </si>
+  <si>
+    <t>Wait for the next section of the registration roadmap to load</t>
+  </si>
+  <si>
+    <t>Select patient country of birth for demographic information</t>
+  </si>
+  <si>
+    <t>cmb_CountryofBirth</t>
+  </si>
+  <si>
+    <t>COUNTRY_OF_BIRTH</t>
+  </si>
+  <si>
+    <t>Select patient nationality for demographic information</t>
+  </si>
+  <si>
+    <t>cmb_Nationality</t>
+  </si>
+  <si>
+    <t>NATIONALITY</t>
+  </si>
+  <si>
+    <t>Select patient ethnicity as a required demographic field</t>
+  </si>
+  <si>
+    <t>cmb_SelectEthnicity</t>
+  </si>
+  <si>
+    <t>ETHNICITY</t>
+  </si>
+  <si>
+    <t>Click Finish to complete the patient registration roadmap and submit all details</t>
+  </si>
+  <si>
+    <t>Wait for NHS number allocation confirmation prompt</t>
+  </si>
+  <si>
+    <t>Click Yes to confirm NHS number allocation for the newly registered patient</t>
+  </si>
+  <si>
+    <t>Wait for visitor status question prompt</t>
+  </si>
+  <si>
+    <t>Click No to confirm patient is not a visitor so NHS number is permanently assigned</t>
+  </si>
+  <si>
+    <t>Wait for registration confirmation popup containing allocated NHS number</t>
+  </si>
+  <si>
+    <t>pageRegConfirmationpopup</t>
+  </si>
+  <si>
+    <t>Capture NHS number from registration confirmation message for reference</t>
+  </si>
+  <si>
+    <t>getTextAndStorePASID</t>
+  </si>
+  <si>
+    <t>_NHSNUMBER</t>
+  </si>
+  <si>
+    <t>Validate NHS number: Verify confirmation message text is not empty confirming NHS number was allocated</t>
+  </si>
+  <si>
+    <t>verifyProperty</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>Click OK to dismiss the registration confirmation popup</t>
+  </si>
+  <si>
+    <t>btn_PopUpOk</t>
+  </si>
+  <si>
+    <t>Wait for home page to reload after patient registration is complete</t>
+  </si>
+  <si>
+    <t>-- NAVIGATE TO PATIENT EPR AND CREATE REFERRAL --</t>
+  </si>
+  <si>
+    <t>Click Find Record to search for the registered patient by surname</t>
+  </si>
+  <si>
+    <t>btn_Findrecord</t>
+  </si>
+  <si>
+    <t>Wait for patient basic search form to load</t>
+  </si>
+  <si>
+    <t>pagePatientBasicSearch</t>
+  </si>
+  <si>
+    <t>Wait for patient search results to load</t>
+  </si>
+  <si>
+    <t>pagePatientSearchGrid</t>
+  </si>
+  <si>
+    <t>lnk_PatientSurname</t>
+  </si>
+  <si>
+    <t>Wait for the patient EPR view to load</t>
+  </si>
+  <si>
+    <t>pageEPRView</t>
+  </si>
+  <si>
+    <t>Validate EPR view loaded: Verify patient PAS ID label is present in the EPR view</t>
+  </si>
+  <si>
+    <t>txt_PASID</t>
+  </si>
+  <si>
+    <t>exists</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>Capture patient PAS ID from EPR view for use in referral and contact workflows</t>
+  </si>
+  <si>
+    <t>_PASID</t>
+  </si>
+  <si>
+    <t>-- CREATE REFERRAL FOR PATIENT --</t>
+  </si>
+  <si>
+    <t>Click Referrals tab in EPR view to navigate to the referrals section</t>
+  </si>
+  <si>
+    <t>btn_Referral</t>
+  </si>
+  <si>
+    <t>Wait for the referrals section to load in EPR view</t>
+  </si>
+  <si>
+    <t>Click Create Referral to initiate a new referral for this patient</t>
+  </si>
+  <si>
+    <t>lnk_CreateReferral</t>
+  </si>
+  <si>
+    <t>Wait for the Create Referral form to load</t>
+  </si>
+  <si>
+    <t>pageCreateReferral</t>
+  </si>
+  <si>
+    <t>Select the service type for the referral</t>
+  </si>
+  <si>
+    <t>cmb_ServiceType</t>
+  </si>
+  <si>
+    <t>SERVICE_TYPE</t>
+  </si>
+  <si>
+    <t>Select the referral source indicating who initiated the referral</t>
+  </si>
+  <si>
+    <t>cmb_RefSource</t>
+  </si>
+  <si>
+    <t>REFERRAL_SOURCE</t>
+  </si>
+  <si>
+    <t>Select the referral priority to indicate urgency</t>
+  </si>
+  <si>
+    <t>cmb_RefPriority</t>
+  </si>
+  <si>
+    <t>REFERRAL_PRIORITY</t>
+  </si>
+  <si>
+    <t>Select the referral type for classification</t>
+  </si>
+  <si>
+    <t>cmb_RefType</t>
+  </si>
+  <si>
+    <t>REFERRAL_TYPE</t>
+  </si>
+  <si>
+    <t>Click Finish Now to complete the referral creation</t>
+  </si>
+  <si>
+    <t>btn_Finishnow</t>
+  </si>
+  <si>
+    <t>Wait for the Additional Options dialog to appear after referral creation</t>
+  </si>
+  <si>
+    <t>pageAdditionaloptionsRef</t>
+  </si>
+  <si>
+    <t>Click Cancel to dismiss the Additional Options dialog and return to EPR view</t>
+  </si>
+  <si>
+    <t>btn_Cancel</t>
+  </si>
+  <si>
+    <t>Wait for EPR view to reload after referral creation is complete</t>
+  </si>
+  <si>
+    <t>-- NAVIGATE TO CARE EVENTS EPR VIEW --</t>
+  </si>
+  <si>
+    <t>Click the EPR tabs down arrow to expand the full list of available EPR tabs</t>
+  </si>
+  <si>
+    <t>pageEPRTab</t>
+  </si>
+  <si>
+    <t>ico_EPRDownArrow</t>
+  </si>
+  <si>
+    <t>Wait for the EPR tab list to expand</t>
+  </si>
+  <si>
+    <t>Click the Care Events tab from the expanded EPR tab list to navigate to Care Events view</t>
+  </si>
+  <si>
+    <t>btn_EPRTab</t>
+  </si>
+  <si>
+    <t>Care events</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events page to load</t>
+  </si>
+  <si>
+    <t>PageCareevents</t>
+  </si>
+  <si>
+    <t>-- CREATE SINGLE CONTACT - PLANNED --</t>
+  </si>
+  <si>
+    <t>Click Create Single Contact from the Care Events task pane to initiate a planned contact</t>
+  </si>
+  <si>
+    <t>lnkSubTaskPaneCreatesinglecontact</t>
+  </si>
+  <si>
+    <t>Wait for the Create Single Contact form to load</t>
+  </si>
+  <si>
+    <t>PageCreatesinglecontact</t>
+  </si>
+  <si>
+    <t>Select the purpose of the planned contact</t>
+  </si>
+  <si>
+    <t>cmb_purpose</t>
+  </si>
+  <si>
+    <t>PURPOSE</t>
+  </si>
+  <si>
+    <t>Select the contact type for the planned single contact</t>
+  </si>
+  <si>
+    <t>cmb_Contacttype</t>
+  </si>
+  <si>
+    <t>CONTACT_TYPE</t>
+  </si>
+  <si>
+    <t>Select the contact subject for the planned single contact</t>
+  </si>
+  <si>
+    <t>cmb_ContactSubject</t>
+  </si>
+  <si>
+    <t>CONTACT_SUBJECT</t>
+  </si>
+  <si>
+    <t>Select the consultation medium indicating how the contact will be conducted</t>
+  </si>
+  <si>
+    <t>cmb_ConsultationMedium</t>
+  </si>
+  <si>
+    <t>CONSULTATION_MEDIUM</t>
+  </si>
+  <si>
+    <t>Select the location type for the planned contact</t>
+  </si>
+  <si>
+    <t>cmb_Locationtype</t>
+  </si>
+  <si>
+    <t>LOCATION_TYPE</t>
+  </si>
+  <si>
+    <t>Click Next to proceed to the date and time step of the Create Single Contact wizard</t>
+  </si>
+  <si>
+    <t>Wait for the next step of the Create Single Contact wizard to load</t>
+  </si>
+  <si>
+    <t>Click Finish Now to complete the Create Single Contact wizard and save as Planned</t>
+  </si>
+  <si>
+    <t>Wait for the document template selection dialog to appear</t>
+  </si>
+  <si>
+    <t>pageDocumentTemplate</t>
+  </si>
+  <si>
+    <t>Click Cancel to dismiss the document template dialog and return to Care Events</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events page to reload after creating the planned contact</t>
+  </si>
+  <si>
+    <t>-- VALIDATE PLANNED STATUS --</t>
+  </si>
+  <si>
+    <t>Validate Planned status: Verify the contact event status shows Planned in the Care Events grid</t>
+  </si>
+  <si>
+    <t>getText</t>
+  </si>
+  <si>
+    <t>-- SELECT PLANNED ENCOUNTER AND RECORD CONTACT - ACTUAL --</t>
+  </si>
+  <si>
+    <t>Select the planned encounter row from the Care Events grid to enable context pane actions</t>
+  </si>
+  <si>
+    <t>toggleElement</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events context pane to update with the selected planned encounter</t>
+  </si>
+  <si>
+    <t>Click Record Contact from the Care Events task pane to record an actual contact for the planned encounter</t>
+  </si>
+  <si>
+    <t>lnkTaskPaneRecordcontact</t>
+  </si>
+  <si>
+    <t>Wait for the Record Contact form to load</t>
+  </si>
+  <si>
+    <t>PageRecordcontact</t>
+  </si>
+  <si>
+    <t>Select the purpose of the actual contact being recorded</t>
+  </si>
+  <si>
+    <t>Select the contact type for the actual contact</t>
+  </si>
+  <si>
+    <t>Select the contact subject for the actual contact</t>
+  </si>
+  <si>
+    <t>Select the consultation medium for how the actual contact was conducted</t>
+  </si>
+  <si>
+    <t>Select the location type for the actual contact</t>
+  </si>
+  <si>
+    <t>Select the outcome of the actual contact</t>
+  </si>
+  <si>
+    <t>cmb_outcome</t>
+  </si>
+  <si>
+    <t>OUTCOME</t>
+  </si>
+  <si>
+    <t>Click Next to proceed to the date and time step of the Record Contact wizard</t>
+  </si>
+  <si>
+    <t>Wait for the next step of the Record Contact wizard to load with date and time fields</t>
+  </si>
+  <si>
+    <t>Click Finish Now to complete the Record Contact wizard and save the actual contact</t>
+  </si>
+  <si>
+    <t>Wait for the confirmation dialog to appear after recording the actual contact</t>
+  </si>
+  <si>
+    <t>pageDialongYesNoPopup</t>
+  </si>
+  <si>
+    <t>Click Yes to confirm and finalise the actual contact recording</t>
+  </si>
+  <si>
+    <t>btn_PopUpYes</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events page to reload after recording the actual contact</t>
+  </si>
+  <si>
+    <t>-- VALIDATE ACTUAL STATUS AFTER RECORD CONTACT --</t>
+  </si>
+  <si>
+    <t>Validate Actual status: Verify the patient event status has updated to Actual in the Care Events grid after Record Contact</t>
+  </si>
+  <si>
+    <t>-- SELECT ACTUAL ENCOUNTER AND MODIFY CONTACT - ACTUAL --</t>
+  </si>
+  <si>
+    <t>Select the actual encounter row from the Care Events grid to enable modify contact action</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events context pane to update with the selected actual encounter</t>
+  </si>
+  <si>
+    <t>Click Modify Contact from the Care Events task pane to modify the actual encounter</t>
+  </si>
+  <si>
+    <t>lnkTaskPaneModifycontact</t>
+  </si>
+  <si>
+    <t>Wait for the Modify Contact form to load with the existing contact details</t>
+  </si>
+  <si>
+    <t>Select the updated purpose for the modified contact</t>
+  </si>
+  <si>
+    <t>Select the updated contact type for the modified contact</t>
+  </si>
+  <si>
+    <t>Select the updated contact subject for the modified contact</t>
+  </si>
+  <si>
+    <t>Select the updated consultation medium for the modified contact</t>
+  </si>
+  <si>
+    <t>Select the updated location type for the modified contact</t>
+  </si>
+  <si>
+    <t>Select the updated outcome for the modified contact</t>
+  </si>
+  <si>
+    <t>Click Next to proceed to the date and time step of the Modify Contact wizard</t>
+  </si>
+  <si>
+    <t>Wait for the next step of the Modify Contact wizard to load</t>
+  </si>
+  <si>
+    <t>Click Finish Now to complete the Modify Contact wizard and close the actual encounter</t>
+  </si>
+  <si>
+    <t>Wait for the confirmation dialog to appear after modifying the contact</t>
+  </si>
+  <si>
+    <t>Click Yes to confirm and finalise the modified contact</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events page to reload after modifying the actual contact</t>
+  </si>
+  <si>
+    <t>-- VALIDATE ACTUAL ENCOUNTER CLOSED AND STATUS UPDATED --</t>
+  </si>
+  <si>
+    <t>Validate Actual encounter closed: Verify the patient event status remains Actual in the Care Events grid confirming the encounter is closed</t>
+  </si>
+  <si>
+    <t>-- VALIDATE ENCOUNTER LIST AND DETAILS --</t>
+  </si>
+  <si>
+    <t>Click to expand the care event row in the list to view sub-encounters</t>
+  </si>
+  <si>
+    <t>Wait for the care event row to expand showing encounter sub-items</t>
+  </si>
+  <si>
+    <t>Click on the Care Event Details link to open the full encounter detail view</t>
+  </si>
+  <si>
+    <t>Wait for the care event detail panel to load with all encounter metadata</t>
+  </si>
+  <si>
+    <t>Validate Encounter Details: Verify that the encounter detail labels (Health Organisation, Encounter Type, Care Provider, Specialty, Start Date, End Date, Encounter ID, Care Provider Role) are visible in the detail panel</t>
+  </si>
+  <si>
+    <t>-- VALIDATE PATIENT EVENT STATUS LIST AND DETAILS --</t>
+  </si>
+  <si>
+    <t>Validate Patient Event Status List: Verify the patient event status in the Care Events list shows Actual confirming all encounters are in the correct status</t>
+  </si>
+  <si>
+    <t>-- RECORD QUICK CONTACT - ACTUAL --</t>
+  </si>
+  <si>
+    <t>Unselect the currently selected encounter row before initiating Quick Contact</t>
+  </si>
+  <si>
+    <t>Click Record Quick Contact from the Care Events task pane to record an immediate actual contact</t>
+  </si>
+  <si>
+    <t>lnkTaskPaneRecordQuickcontact</t>
+  </si>
+  <si>
+    <t>Wait for the Record Quick Contact form to load</t>
+  </si>
+  <si>
+    <t>PageRecordquickcontact</t>
+  </si>
+  <si>
+    <t>Select the purpose for the quick contact</t>
+  </si>
+  <si>
+    <t>Select the contact type for the quick contact</t>
+  </si>
+  <si>
+    <t>Select the location type for the quick contact</t>
+  </si>
+  <si>
+    <t>Click Select Existing Referral icon to associate this quick contact with the created referral</t>
+  </si>
+  <si>
+    <t>ico_SelectExistingreferral</t>
+  </si>
+  <si>
+    <t>Wait for the referral search results to load in the selection dialog</t>
+  </si>
+  <si>
+    <t>Click Select to add the existing referral to the quick contact</t>
+  </si>
+  <si>
+    <t>btn_ReferralSFS</t>
+  </si>
+  <si>
+    <t>Wait for the quick contact form to reload with the selected referral populated</t>
+  </si>
+  <si>
+    <t>Select the outcome for the quick contact</t>
+  </si>
+  <si>
+    <t>Click Finish Now to complete the Record Quick Contact wizard and save the actual contact</t>
+  </si>
+  <si>
+    <t>Wait for the Care Events page to reload after recording the quick contact</t>
+  </si>
+  <si>
+    <t>-- VALIDATE QUICK CONTACT ACTUAL STATUS --</t>
+  </si>
+  <si>
+    <t>Validate Quick Contact Actual status: Verify the patient event status shows Actual in the Care Events grid after recording the quick contact</t>
+  </si>
+  <si>
+    <t>-- LOGOUT --</t>
+  </si>
+  <si>
+    <t>Click Logout button to initiate logout from Lorenzo application</t>
+  </si>
+  <si>
+    <t>btn_Logout</t>
+  </si>
+  <si>
+    <t>Confirm logout by clicking Yes on the logout confirmation dialog</t>
+  </si>
+  <si>
+    <t>txt_Yes</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>British</t>
+  </si>
+  <si>
+    <t>Community Mental Health</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Face to face</t>
+  </si>
+  <si>
+    <t>Initial Assessment</t>
+  </si>
+  <si>
+    <t>Face to Face</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Appointment attended</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>LSTP_Contacts_WF001</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Contacts</t>
+  </si>
+  <si>
+    <t>Sub-Module</t>
+  </si>
+  <si>
+    <t>Care Events EPR View - Contact Lifecycle Management</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>End-to-end verification of the Contacts module covering new patient registration, referral creation, navigation to Care Events EPR view, creating a planned single contact, recording as actual, modifying the actual contact, validating encounter list and patient event status details, recording a quick actual contact with referral association, and final status validation</t>
+  </si>
+  <si>
+    <t>Complexity</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Estimated Duration</t>
+  </si>
+  <si>
+    <t>30-35 minutes</t>
+  </si>
+  <si>
+    <t>Total Steps</t>
+  </si>
+  <si>
+    <t>Total Pages</t>
+  </si>
+  <si>
+    <t>Total Elements</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>KDF Generator</t>
+  </si>
+  <si>
+    <t>Created Date</t>
+  </si>
+  <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>Prerequisites</t>
+  </si>
+  <si>
+    <t>Lorenzo Contacts module enabled, patient registration rights available, referral creation rights available, Care Events EPR view accessible, contact types and purposes configured, document template configured for contacts</t>
+  </si>
+  <si>
+    <t>Test Data Variables</t>
+  </si>
+  <si>
+    <t>FORENAME, CITY, COUNTRY, COUNTRY_OF_BIRTH, NATIONALITY, ETHNICITY, SERVICE_TYPE, REFERRAL_SOURCE, REFERRAL_PRIORITY, REFERRAL_TYPE, PURPOSE, CONTACT_TYPE, CONTACT_SUBJECT, CONSULTATION_MEDIUM, LOCATION_TYPE, OUTCOME</t>
+  </si>
+  <si>
+    <t>Assertions</t>
+  </si>
+  <si>
+    <t>Pages Used</t>
+  </si>
+  <si>
+    <t>pageLogin, pageHome, pageSearchPatient, pageRoadMapButtons, pagePatientSearchResult, pageRegRegistration, pageWarning - LORENZO, pageQuestion - LORENZO, pageRegConfirmationpopup, pagePatientBasicSearch, pagePatientSearchGrid, pageEPRView, pageCreateReferral, pageAdditionaloptionsRef, pageEPRTab, PageCareevents, PageCreatesinglecontact, pageDocumentTemplate, PageRecordcontact, pageDialongYesNoPopup, PageRecordquickcontact</t>
+  </si>
+  <si>
+    <t>Workflows Covered</t>
+  </si>
+  <si>
+    <t>Login + Patient Registration (Full Roadmap 2 Sections) + NHS Allocation + Navigate Back to Patient EPR + Capture PAS ID + Create Referral + Navigate Care Events EPR View + Create Single Contact (Planned) + Validate Planned Status + Select Planned Encounter + Record Contact (Actual) + Validate Actual Status + Select Actual Encounter + Modify Contact (Actual) + Validate Actual Encounter Closed + Validate Encounter List and Details + Validate Patient Event Status + Record Quick Contact (Actual with Referral) + Validate Quick Contact Actual Status + Logout</t>
+  </si>
+  <si>
+    <t>VariableName</t>
+  </si>
+  <si>
+    <t>SampleValue</t>
+  </si>
+  <si>
+    <t>Auto-generated surname used for new patient registration to ensure uniqueness</t>
+  </si>
+  <si>
+    <t>AutoGenerated</t>
+  </si>
+  <si>
+    <t>NHS number captured from registration confirmation popup</t>
+  </si>
+  <si>
+    <t>Captured at runtime</t>
+  </si>
+  <si>
+    <t>PAS ID captured from patient EPR view after registration, used for reference</t>
+  </si>
+  <si>
+    <t>_USERNAME</t>
+  </si>
+  <si>
+    <t>Login username from environment configuration</t>
+  </si>
+  <si>
+    <t>From config</t>
+  </si>
+  <si>
+    <t>_PASSWORD</t>
+  </si>
+  <si>
+    <t>Login password from environment configuration</t>
+  </si>
+  <si>
+    <t>Click Find record to open the patient search form</t>
+  </si>
+  <si>
+    <t>lnkTaskPanePatient</t>
+  </si>
+  <si>
+    <t>Enter generated surname in search</t>
+  </si>
+  <si>
+    <t>Select Gender in search</t>
+  </si>
+  <si>
+    <t>cmb_Gender</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Set focus in DOB field</t>
+  </si>
+  <si>
+    <t>txt_DOB</t>
+  </si>
+  <si>
+    <t>Set date of birth</t>
+  </si>
+  <si>
+    <t>29/08/1982</t>
+  </si>
+  <si>
+    <t>Wait before Find</t>
+  </si>
+  <si>
+    <t>Click Find to search</t>
+  </si>
+  <si>
+    <t>Select patient country of registration</t>
   </si>
   <si>
     <t>txt_Forename</t>
   </si>
   <si>
-    <t>FORENAME</t>
-  </si>
-  <si>
-    <t>Enter patient surname in the registration form using generated random surname</t>
-  </si>
-  <si>
-    <t>Enter patient city of residence in the registration address fields</t>
+    <t>Enter forename in search (mandatory)</t>
+  </si>
+  <si>
+    <t>Wait for registration form to load</t>
+  </si>
+  <si>
+    <t>Launch Registration (handle PDS timeout, open reg form)</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>Enter City (mandatory)</t>
   </si>
   <si>
     <t>txt_City</t>
   </si>
   <si>
-    <t>CITY</t>
-  </si>
-  <si>
-    <t>Select patient country of residence in the registration address fields</t>
-  </si>
-  <si>
-    <t>cmb_Country</t>
-  </si>
-  <si>
-    <t>selectComboBox</t>
-  </si>
-  <si>
-    <t>COUNTRY</t>
-  </si>
-  <si>
-    <t>Click Next to proceed to the second section of the registration roadmap</t>
-  </si>
-  <si>
-    <t>btn_Next</t>
-  </si>
-  <si>
-    <t>-- PATIENT REGISTRATION ROADMAP - SECTION 2: ADDITIONAL DEMOGRAPHICS --</t>
-  </si>
-  <si>
-    <t>Wait for the next section of the registration roadmap to load</t>
-  </si>
-  <si>
-    <t>Select patient country of birth for demographic information</t>
-  </si>
-  <si>
-    <t>cmb_CountryofBirth</t>
-  </si>
-  <si>
-    <t>COUNTRY_OF_BIRTH</t>
-  </si>
-  <si>
-    <t>Select patient nationality for demographic information</t>
-  </si>
-  <si>
-    <t>cmb_Nationality</t>
-  </si>
-  <si>
-    <t>NATIONALITY</t>
-  </si>
-  <si>
-    <t>Select patient ethnicity as a required demographic field</t>
-  </si>
-  <si>
-    <t>cmb_SelectEthnicity</t>
-  </si>
-  <si>
-    <t>ETHNICITY</t>
-  </si>
-  <si>
-    <t>Click Finish to complete the patient registration roadmap and submit all details</t>
-  </si>
-  <si>
-    <t>btn_Finish</t>
-  </si>
-  <si>
-    <t>Wait for NHS number allocation confirmation prompt</t>
-  </si>
-  <si>
-    <t>pageWarning - LORENZO</t>
-  </si>
-  <si>
-    <t>Click Yes to confirm NHS number allocation for the newly registered patient</t>
-  </si>
-  <si>
-    <t>btn_NHSYes</t>
-  </si>
-  <si>
-    <t>Wait for visitor status question prompt</t>
-  </si>
-  <si>
-    <t>pageQuestion - LORENZO</t>
-  </si>
-  <si>
-    <t>Click No to confirm patient is not a visitor so NHS number is permanently assigned</t>
-  </si>
-  <si>
-    <t>btn_NHSNo</t>
-  </si>
-  <si>
-    <t>Wait for registration confirmation popup containing allocated NHS number</t>
-  </si>
-  <si>
-    <t>pageRegConfirmationpopup</t>
-  </si>
-  <si>
-    <t>Capture NHS number from registration confirmation message for reference</t>
-  </si>
-  <si>
-    <t>lbl_ConfirmationText</t>
-  </si>
-  <si>
-    <t>getTextAndStorePASID</t>
-  </si>
-  <si>
-    <t>_NHSNUMBER</t>
-  </si>
-  <si>
-    <t>Validate NHS number: Verify confirmation message text is not empty confirming NHS number was allocated</t>
-  </si>
-  <si>
-    <t>verifyProperty</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>notEmpty</t>
-  </si>
-  <si>
-    <t>Click OK to dismiss the registration confirmation popup</t>
-  </si>
-  <si>
-    <t>btn_PopUpOk</t>
-  </si>
-  <si>
-    <t>Wait for home page to reload after patient registration is complete</t>
-  </si>
-  <si>
-    <t>-- NAVIGATE TO PATIENT EPR AND CREATE REFERRAL --</t>
-  </si>
-  <si>
-    <t>Click Find Record to search for the registered patient by surname</t>
-  </si>
-  <si>
-    <t>btn_Findrecord</t>
-  </si>
-  <si>
-    <t>Wait for patient basic search form to load</t>
-  </si>
-  <si>
-    <t>pagePatientBasicSearch</t>
-  </si>
-  <si>
-    <t>Enter the registered patient surname to locate the newly created record</t>
-  </si>
-  <si>
-    <t>Click Find to search for the registered patient</t>
-  </si>
-  <si>
-    <t>Wait for patient search results to load</t>
-  </si>
-  <si>
-    <t>Click patient surname link to open the patient EPR view</t>
-  </si>
-  <si>
-    <t>pagePatientSearchGrid</t>
-  </si>
-  <si>
-    <t>lnk_PatientSurname</t>
-  </si>
-  <si>
-    <t>Wait for the patient EPR view to load</t>
-  </si>
-  <si>
-    <t>pageEPRView</t>
-  </si>
-  <si>
-    <t>Validate EPR view loaded: Verify patient PAS ID label is present in the EPR view</t>
-  </si>
-  <si>
-    <t>txt_PASID</t>
-  </si>
-  <si>
-    <t>exists</t>
-  </si>
-  <si>
-    <t>equal</t>
-  </si>
-  <si>
-    <t>Capture patient PAS ID from EPR view for use in referral and contact workflows</t>
-  </si>
-  <si>
-    <t>_PASID</t>
-  </si>
-  <si>
-    <t>-- CREATE REFERRAL FOR PATIENT --</t>
-  </si>
-  <si>
-    <t>Click Referrals tab in EPR view to navigate to the referrals section</t>
-  </si>
-  <si>
-    <t>btn_Referral</t>
-  </si>
-  <si>
-    <t>Wait for the referrals section to load in EPR view</t>
-  </si>
-  <si>
-    <t>Click Create Referral to initiate a new referral for this patient</t>
-  </si>
-  <si>
-    <t>lnk_CreateReferral</t>
-  </si>
-  <si>
-    <t>Wait for the Create Referral form to load</t>
-  </si>
-  <si>
-    <t>pageCreateReferral</t>
-  </si>
-  <si>
-    <t>Select the service type for the referral</t>
-  </si>
-  <si>
-    <t>cmb_ServiceType</t>
-  </si>
-  <si>
-    <t>SERVICE_TYPE</t>
-  </si>
-  <si>
-    <t>Select the referral source indicating who initiated the referral</t>
-  </si>
-  <si>
-    <t>cmb_RefSource</t>
-  </si>
-  <si>
-    <t>REFERRAL_SOURCE</t>
-  </si>
-  <si>
-    <t>Select the referral priority to indicate urgency</t>
-  </si>
-  <si>
-    <t>cmb_RefPriority</t>
-  </si>
-  <si>
-    <t>REFERRAL_PRIORITY</t>
-  </si>
-  <si>
-    <t>Select the referral type for classification</t>
-  </si>
-  <si>
-    <t>cmb_RefType</t>
-  </si>
-  <si>
-    <t>REFERRAL_TYPE</t>
-  </si>
-  <si>
-    <t>Click Finish Now to complete the referral creation</t>
-  </si>
-  <si>
-    <t>btn_Finishnow</t>
-  </si>
-  <si>
-    <t>Wait for the Additional Options dialog to appear after referral creation</t>
-  </si>
-  <si>
-    <t>pageAdditionaloptionsRef</t>
-  </si>
-  <si>
-    <t>Click Cancel to dismiss the Additional Options dialog and return to EPR view</t>
-  </si>
-  <si>
-    <t>btn_Cancel</t>
-  </si>
-  <si>
-    <t>Wait for EPR view to reload after referral creation is complete</t>
-  </si>
-  <si>
-    <t>-- NAVIGATE TO CARE EVENTS EPR VIEW --</t>
-  </si>
-  <si>
-    <t>Click the EPR tabs down arrow to expand the full list of available EPR tabs</t>
-  </si>
-  <si>
-    <t>pageEPRTab</t>
-  </si>
-  <si>
-    <t>ico_EPRDownArrow</t>
-  </si>
-  <si>
-    <t>Wait for the EPR tab list to expand</t>
-  </si>
-  <si>
-    <t>Click the Care Events tab from the expanded EPR tab list to navigate to Care Events view</t>
-  </si>
-  <si>
-    <t>btn_EPRTab</t>
-  </si>
-  <si>
-    <t>Care events</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events page to load</t>
-  </si>
-  <si>
-    <t>PageCareevents</t>
-  </si>
-  <si>
-    <t>-- CREATE SINGLE CONTACT - PLANNED --</t>
-  </si>
-  <si>
-    <t>Click Create Single Contact from the Care Events task pane to initiate a planned contact</t>
-  </si>
-  <si>
-    <t>lnkSubTaskPaneCreatesinglecontact</t>
-  </si>
-  <si>
-    <t>Wait for the Create Single Contact form to load</t>
-  </si>
-  <si>
-    <t>PageCreatesinglecontact</t>
-  </si>
-  <si>
-    <t>Select the purpose of the planned contact</t>
-  </si>
-  <si>
-    <t>cmb_purpose</t>
-  </si>
-  <si>
-    <t>PURPOSE</t>
-  </si>
-  <si>
-    <t>Select the contact type for the planned single contact</t>
-  </si>
-  <si>
-    <t>cmb_Contacttype</t>
-  </si>
-  <si>
-    <t>CONTACT_TYPE</t>
-  </si>
-  <si>
-    <t>Select the contact subject for the planned single contact</t>
-  </si>
-  <si>
-    <t>cmb_ContactSubject</t>
-  </si>
-  <si>
-    <t>CONTACT_SUBJECT</t>
-  </si>
-  <si>
-    <t>Select the consultation medium indicating how the contact will be conducted</t>
-  </si>
-  <si>
-    <t>cmb_ConsultationMedium</t>
-  </si>
-  <si>
-    <t>CONSULTATION_MEDIUM</t>
-  </si>
-  <si>
-    <t>Select the location type for the planned contact</t>
-  </si>
-  <si>
-    <t>cmb_Locationtype</t>
-  </si>
-  <si>
-    <t>LOCATION_TYPE</t>
-  </si>
-  <si>
-    <t>Click Next to proceed to the date and time step of the Create Single Contact wizard</t>
-  </si>
-  <si>
-    <t>Wait for the next step of the Create Single Contact wizard to load</t>
-  </si>
-  <si>
-    <t>Click Finish Now to complete the Create Single Contact wizard and save as Planned</t>
-  </si>
-  <si>
-    <t>Wait for the document template selection dialog to appear</t>
-  </si>
-  <si>
-    <t>pageDocumentTemplate</t>
-  </si>
-  <si>
-    <t>Click Cancel to dismiss the document template dialog and return to Care Events</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events page to reload after creating the planned contact</t>
-  </si>
-  <si>
-    <t>-- VALIDATE PLANNED STATUS --</t>
-  </si>
-  <si>
-    <t>Validate Planned status: Verify the contact event status shows Planned in the Care Events grid</t>
-  </si>
-  <si>
-    <t>getText</t>
-  </si>
-  <si>
-    <t>-- SELECT PLANNED ENCOUNTER AND RECORD CONTACT - ACTUAL --</t>
-  </si>
-  <si>
-    <t>Select the planned encounter row from the Care Events grid to enable context pane actions</t>
-  </si>
-  <si>
-    <t>toggleElement</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events context pane to update with the selected planned encounter</t>
-  </si>
-  <si>
-    <t>Click Record Contact from the Care Events task pane to record an actual contact for the planned encounter</t>
-  </si>
-  <si>
-    <t>lnkTaskPaneRecordcontact</t>
-  </si>
-  <si>
-    <t>Wait for the Record Contact form to load</t>
-  </si>
-  <si>
-    <t>PageRecordcontact</t>
-  </si>
-  <si>
-    <t>Select the purpose of the actual contact being recorded</t>
-  </si>
-  <si>
-    <t>Select the contact type for the actual contact</t>
-  </si>
-  <si>
-    <t>Select the contact subject for the actual contact</t>
-  </si>
-  <si>
-    <t>Select the consultation medium for how the actual contact was conducted</t>
-  </si>
-  <si>
-    <t>Select the location type for the actual contact</t>
-  </si>
-  <si>
-    <t>Select the outcome of the actual contact</t>
-  </si>
-  <si>
-    <t>cmb_outcome</t>
-  </si>
-  <si>
-    <t>OUTCOME</t>
-  </si>
-  <si>
-    <t>Click Next to proceed to the date and time step of the Record Contact wizard</t>
-  </si>
-  <si>
-    <t>Wait for the next step of the Record Contact wizard to load with date and time fields</t>
-  </si>
-  <si>
-    <t>Click Finish Now to complete the Record Contact wizard and save the actual contact</t>
-  </si>
-  <si>
-    <t>Wait for the confirmation dialog to appear after recording the actual contact</t>
-  </si>
-  <si>
-    <t>pageDialongYesNoPopup</t>
-  </si>
-  <si>
-    <t>Click Yes to confirm and finalise the actual contact recording</t>
-  </si>
-  <si>
-    <t>btn_PopUpYes</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events page to reload after recording the actual contact</t>
-  </si>
-  <si>
-    <t>-- VALIDATE ACTUAL STATUS AFTER RECORD CONTACT --</t>
-  </si>
-  <si>
-    <t>Validate Actual status: Verify the patient event status has updated to Actual in the Care Events grid after Record Contact</t>
-  </si>
-  <si>
-    <t>-- SELECT ACTUAL ENCOUNTER AND MODIFY CONTACT - ACTUAL --</t>
-  </si>
-  <si>
-    <t>Select the actual encounter row from the Care Events grid to enable modify contact action</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events context pane to update with the selected actual encounter</t>
-  </si>
-  <si>
-    <t>Click Modify Contact from the Care Events task pane to modify the actual encounter</t>
-  </si>
-  <si>
-    <t>lnkTaskPaneModifycontact</t>
-  </si>
-  <si>
-    <t>Wait for the Modify Contact form to load with the existing contact details</t>
-  </si>
-  <si>
-    <t>Select the updated purpose for the modified contact</t>
-  </si>
-  <si>
-    <t>Select the updated contact type for the modified contact</t>
-  </si>
-  <si>
-    <t>Select the updated contact subject for the modified contact</t>
-  </si>
-  <si>
-    <t>Select the updated consultation medium for the modified contact</t>
-  </si>
-  <si>
-    <t>Select the updated location type for the modified contact</t>
-  </si>
-  <si>
-    <t>Select the updated outcome for the modified contact</t>
-  </si>
-  <si>
-    <t>Click Next to proceed to the date and time step of the Modify Contact wizard</t>
-  </si>
-  <si>
-    <t>Wait for the next step of the Modify Contact wizard to load</t>
-  </si>
-  <si>
-    <t>Click Finish Now to complete the Modify Contact wizard and close the actual encounter</t>
-  </si>
-  <si>
-    <t>Wait for the confirmation dialog to appear after modifying the contact</t>
-  </si>
-  <si>
-    <t>Click Yes to confirm and finalise the modified contact</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events page to reload after modifying the actual contact</t>
-  </si>
-  <si>
-    <t>-- VALIDATE ACTUAL ENCOUNTER CLOSED AND STATUS UPDATED --</t>
-  </si>
-  <si>
-    <t>Validate Actual encounter closed: Verify the patient event status remains Actual in the Care Events grid confirming the encounter is closed</t>
-  </si>
-  <si>
-    <t>-- VALIDATE ENCOUNTER LIST AND DETAILS --</t>
-  </si>
-  <si>
-    <t>Click to expand the care event row in the list to view sub-encounters</t>
-  </si>
-  <si>
-    <t>Wait for the care event row to expand showing encounter sub-items</t>
-  </si>
-  <si>
-    <t>Click on the Care Event Details link to open the full encounter detail view</t>
-  </si>
-  <si>
-    <t>Wait for the care event detail panel to load with all encounter metadata</t>
-  </si>
-  <si>
-    <t>Validate Encounter Details: Verify that the encounter detail labels (Health Organisation, Encounter Type, Care Provider, Specialty, Start Date, End Date, Encounter ID, Care Provider Role) are visible in the detail panel</t>
-  </si>
-  <si>
-    <t>-- VALIDATE PATIENT EVENT STATUS LIST AND DETAILS --</t>
-  </si>
-  <si>
-    <t>Validate Patient Event Status List: Verify the patient event status in the Care Events list shows Actual confirming all encounters are in the correct status</t>
-  </si>
-  <si>
-    <t>-- RECORD QUICK CONTACT - ACTUAL --</t>
-  </si>
-  <si>
-    <t>Unselect the currently selected encounter row before initiating Quick Contact</t>
-  </si>
-  <si>
-    <t>Click Record Quick Contact from the Care Events task pane to record an immediate actual contact</t>
-  </si>
-  <si>
-    <t>lnkTaskPaneRecordQuickcontact</t>
-  </si>
-  <si>
-    <t>Wait for the Record Quick Contact form to load</t>
-  </si>
-  <si>
-    <t>PageRecordquickcontact</t>
-  </si>
-  <si>
-    <t>Select the purpose for the quick contact</t>
-  </si>
-  <si>
-    <t>Select the contact type for the quick contact</t>
-  </si>
-  <si>
-    <t>Select the location type for the quick contact</t>
-  </si>
-  <si>
-    <t>Click Select Existing Referral icon to associate this quick contact with the created referral</t>
-  </si>
-  <si>
-    <t>ico_SelectExistingreferral</t>
-  </si>
-  <si>
-    <t>Wait for the referral search results to load in the selection dialog</t>
-  </si>
-  <si>
-    <t>Click Select to add the existing referral to the quick contact</t>
-  </si>
-  <si>
-    <t>btn_ReferralSFS</t>
-  </si>
-  <si>
-    <t>Wait for the quick contact form to reload with the selected referral populated</t>
-  </si>
-  <si>
-    <t>Select the outcome for the quick contact</t>
-  </si>
-  <si>
-    <t>Click Finish Now to complete the Record Quick Contact wizard and save the actual contact</t>
-  </si>
-  <si>
-    <t>Wait for the Care Events page to reload after recording the quick contact</t>
-  </si>
-  <si>
-    <t>-- VALIDATE QUICK CONTACT ACTUAL STATUS --</t>
-  </si>
-  <si>
-    <t>Validate Quick Contact Actual status: Verify the patient event status shows Actual in the Care Events grid after recording the quick contact</t>
-  </si>
-  <si>
-    <t>-- LOGOUT --</t>
-  </si>
-  <si>
-    <t>Click Logout button to initiate logout from Lorenzo application</t>
-  </si>
-  <si>
-    <t>btn_Logout</t>
-  </si>
-  <si>
-    <t>Confirm logout by clicking Yes on the logout confirmation dialog</t>
-  </si>
-  <si>
-    <t>txt_Yes</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>British</t>
-  </si>
-  <si>
-    <t>A - White British</t>
-  </si>
-  <si>
-    <t>Community Mental Health</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>Routine</t>
-  </si>
-  <si>
-    <t>Internal</t>
-  </si>
-  <si>
-    <t>Assessment</t>
-  </si>
-  <si>
-    <t>Face to face</t>
-  </si>
-  <si>
-    <t>Initial Assessment</t>
-  </si>
-  <si>
-    <t>Face to Face</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Appointment attended</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>LSTP_Contacts_WF001</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Contacts</t>
-  </si>
-  <si>
-    <t>Sub-Module</t>
-  </si>
-  <si>
-    <t>Care Events EPR View - Contact Lifecycle Management</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>End-to-end verification of the Contacts module covering new patient registration, referral creation, navigation to Care Events EPR view, creating a planned single contact, recording as actual, modifying the actual contact, validating encounter list and patient event status details, recording a quick actual contact with referral association, and final status validation</t>
-  </si>
-  <si>
-    <t>Complexity</t>
-  </si>
-  <si>
-    <t>Very High</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>Estimated Duration</t>
-  </si>
-  <si>
-    <t>30-35 minutes</t>
-  </si>
-  <si>
-    <t>Total Steps</t>
-  </si>
-  <si>
-    <t>Total Pages</t>
-  </si>
-  <si>
-    <t>Total Elements</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>KDF Generator</t>
-  </si>
-  <si>
-    <t>Created Date</t>
-  </si>
-  <si>
-    <t>Last Updated</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ready</t>
-  </si>
-  <si>
-    <t>Prerequisites</t>
-  </si>
-  <si>
-    <t>Lorenzo Contacts module enabled, patient registration rights available, referral creation rights available, Care Events EPR view accessible, contact types and purposes configured, document template configured for contacts</t>
-  </si>
-  <si>
-    <t>Test Data Variables</t>
-  </si>
-  <si>
-    <t>FORENAME, CITY, COUNTRY, COUNTRY_OF_BIRTH, NATIONALITY, ETHNICITY, SERVICE_TYPE, REFERRAL_SOURCE, REFERRAL_PRIORITY, REFERRAL_TYPE, PURPOSE, CONTACT_TYPE, CONTACT_SUBJECT, CONSULTATION_MEDIUM, LOCATION_TYPE, OUTCOME</t>
-  </si>
-  <si>
-    <t>Assertions</t>
-  </si>
-  <si>
-    <t>Pages Used</t>
-  </si>
-  <si>
-    <t>pageLogin, pageHome, pageSearchPatient, pageRoadMapButtons, pagePatientSearchResult, pageRegRegistration, pageWarning - LORENZO, pageQuestion - LORENZO, pageRegConfirmationpopup, pagePatientBasicSearch, pagePatientSearchGrid, pageEPRView, pageCreateReferral, pageAdditionaloptionsRef, pageEPRTab, PageCareevents, PageCreatesinglecontact, pageDocumentTemplate, PageRecordcontact, pageDialongYesNoPopup, PageRecordquickcontact</t>
-  </si>
-  <si>
-    <t>Workflows Covered</t>
-  </si>
-  <si>
-    <t>Login + Patient Registration (Full Roadmap 2 Sections) + NHS Allocation + Navigate Back to Patient EPR + Capture PAS ID + Create Referral + Navigate Care Events EPR View + Create Single Contact (Planned) + Validate Planned Status + Select Planned Encounter + Record Contact (Actual) + Validate Actual Status + Select Actual Encounter + Modify Contact (Actual) + Validate Actual Encounter Closed + Validate Encounter List and Details + Validate Patient Event Status + Record Quick Contact (Actual with Referral) + Validate Quick Contact Actual Status + Logout</t>
-  </si>
-  <si>
-    <t>VariableName</t>
-  </si>
-  <si>
-    <t>SampleValue</t>
-  </si>
-  <si>
-    <t>Auto-generated surname used for new patient registration to ensure uniqueness</t>
-  </si>
-  <si>
-    <t>AutoGenerated</t>
-  </si>
-  <si>
-    <t>NHS number captured from registration confirmation popup</t>
-  </si>
-  <si>
-    <t>Captured at runtime</t>
-  </si>
-  <si>
-    <t>PAS ID captured from patient EPR view after registration, used for reference</t>
-  </si>
-  <si>
-    <t>_USERNAME</t>
-  </si>
-  <si>
-    <t>Login username from environment configuration</t>
-  </si>
-  <si>
-    <t>From config</t>
-  </si>
-  <si>
-    <t>_PASSWORD</t>
-  </si>
-  <si>
-    <t>Login password from environment configuration</t>
-  </si>
-  <si>
-    <t>Click Find record to open the patient search form</t>
-  </si>
-  <si>
-    <t>lnkTaskPanePatient</t>
+    <t>Solihull</t>
+  </si>
+  <si>
+    <t>Dismiss validate-address dialog (Ok = save anyway)</t>
+  </si>
+  <si>
+    <t>btn_OK</t>
+  </si>
+  <si>
+    <t>Wait for address validation</t>
+  </si>
+  <si>
+    <t>Click Next to advance to Add social information</t>
+  </si>
+  <si>
+    <t>Cancel the address finder dialog</t>
+  </si>
+  <si>
+    <t>btn_AddrCancel</t>
+  </si>
+  <si>
+    <t>Wait after cancelling address finder</t>
+  </si>
+  <si>
+    <t>White - British</t>
+  </si>
+  <si>
+    <t>btn_PopUpNo</t>
+  </si>
+  <si>
+    <t>lbl_ConfirmationTextTemp</t>
+  </si>
+  <si>
+    <t>notequals</t>
+  </si>
+  <si>
+    <t>Cancel the 'Select document templates' dialog to proceed</t>
+  </si>
+  <si>
+    <t>btn_PopUpDocCancel</t>
+  </si>
+  <si>
+    <t>Enter patient surname in search</t>
+  </si>
+  <si>
+    <t>lbl_Gender</t>
+  </si>
+  <si>
+    <t>Enter Date of birth in search</t>
+  </si>
+  <si>
+    <t>Submit patient search by pressing Enter</t>
+  </si>
+  <si>
+    <t>sendKeys</t>
+  </si>
+  <si>
+    <t>ENTER</t>
+  </si>
+  <si>
+    <t>Click patient surname to select record (triggers PDS trace)</t>
+  </si>
+  <si>
+    <t>Dismiss PDS Trace timeout - click No to decouple and open EPR</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2C8E55-67E3-4639-8044-17114017BF27}">
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -1455,25 +1491,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1481,13 +1514,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1495,10 +1528,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1509,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1526,13 +1559,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1540,16 +1573,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1557,13 +1590,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
         <v>28</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1571,19 +1604,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="J10" t="s">
         <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1591,16 +1624,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1608,13 +1644,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>303</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="J12" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1622,19 +1664,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
+        <v>297</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1642,13 +1681,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>297</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="J14" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1656,13 +1701,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>300</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1670,19 +1718,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>301</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1690,18 +1735,12 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" t="s">
+        <v>307</v>
+      </c>
+      <c r="K17" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1710,19 +1749,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>305</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1730,19 +1763,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>308</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" t="s">
-        <v>55</v>
+        <v>30</v>
+      </c>
+      <c r="J19" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1750,16 +1783,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>302</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K20" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1767,13 +1803,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1781,13 +1820,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>311</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>312</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1795,19 +1837,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>315</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>316</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="K23" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1815,19 +1854,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="K24" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1835,19 +1868,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="K25" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1855,16 +1882,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1872,13 +1899,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1886,16 +1913,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1903,13 +1927,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1917,16 +1947,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K30" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1934,13 +1967,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K31" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1948,19 +1987,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>83</v>
-      </c>
-      <c r="J32" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1968,22 +2004,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
-      </c>
-      <c r="G33" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1991,16 +2018,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2008,13 +2035,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" t="s">
         <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2022,13 +2049,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" t="s">
+        <v>319</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2036,16 +2066,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" t="s">
         <v>19</v>
-      </c>
-      <c r="D37" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2053,13 +2080,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>320</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="J38" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2067,19 +2100,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" t="s">
-        <v>34</v>
+        <v>63</v>
+      </c>
+      <c r="G39" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2087,16 +2123,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2104,13 +2140,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>322</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>171</v>
+      </c>
+      <c r="D41" t="s">
+        <v>323</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2118,16 +2157,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2135,13 +2171,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2149,25 +2185,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
-      </c>
-      <c r="G44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H44" t="s">
-        <v>108</v>
-      </c>
-      <c r="J44" t="b">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2175,19 +2202,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>83</v>
-      </c>
-      <c r="J45" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2195,13 +2216,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>324</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" t="s">
+        <v>29</v>
       </c>
       <c r="F46" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="J46" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2209,30 +2236,33 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>293</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>325</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="J47" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>114</v>
-      </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>72</v>
+      </c>
+      <c r="D48" t="s">
+        <v>297</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2240,16 +2270,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>326</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>297</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="J49" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2257,13 +2290,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>327</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>72</v>
+      </c>
+      <c r="D50" t="s">
+        <v>297</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>328</v>
+      </c>
+      <c r="J50" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2271,19 +2310,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F51" t="s">
-        <v>54</v>
-      </c>
-      <c r="K51" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2291,19 +2324,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
-      </c>
-      <c r="K52" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2311,19 +2341,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>331</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>319</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
-      </c>
-      <c r="K53" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2331,19 +2358,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
-      </c>
-      <c r="K54" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2351,16 +2372,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="G55" t="s">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2368,13 +2398,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="J56" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2382,16 +2418,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
-      </c>
-      <c r="C57" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2399,13 +2432,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>77</v>
+      </c>
+      <c r="D58" t="s">
+        <v>86</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2413,13 +2449,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>77</v>
       </c>
       <c r="F59" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2427,16 +2463,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="D60" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="F60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2444,13 +2480,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="C61" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2458,19 +2494,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E62" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K62" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2478,13 +2514,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>91</v>
+      </c>
+      <c r="D63" t="s">
+        <v>96</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K63" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2492,13 +2534,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>98</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" t="s">
+        <v>99</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K64" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2506,16 +2554,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K65" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2523,13 +2574,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>91</v>
+      </c>
+      <c r="D66" t="s">
+        <v>105</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2537,19 +2591,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="C67" t="s">
-        <v>152</v>
-      </c>
-      <c r="D67" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="F67" t="s">
-        <v>54</v>
-      </c>
-      <c r="K67" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2557,19 +2605,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="F68" t="s">
-        <v>54</v>
-      </c>
-      <c r="K68" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2577,19 +2622,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="C69" t="s">
-        <v>152</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="F69" t="s">
-        <v>54</v>
-      </c>
-      <c r="K69" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2597,19 +2636,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" t="s">
-        <v>152</v>
-      </c>
-      <c r="D70" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F70" t="s">
-        <v>54</v>
-      </c>
-      <c r="K70" t="s">
-        <v>164</v>
+        <v>21</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2617,19 +2650,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>54</v>
-      </c>
-      <c r="K71" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2637,16 +2667,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2654,13 +2681,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>113</v>
+      </c>
+      <c r="D73" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" t="s">
+        <v>118</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2668,16 +2701,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
-      </c>
-      <c r="D74" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2685,13 +2715,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -2702,16 +2729,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2719,13 +2746,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="C77" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2733,13 +2760,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>126</v>
+      </c>
+      <c r="C78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" t="s">
+        <v>127</v>
       </c>
       <c r="F78" t="s">
-        <v>22</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K78" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2747,25 +2780,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="C79" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="F79" t="s">
-        <v>86</v>
-      </c>
-      <c r="G79" t="s">
-        <v>107</v>
-      </c>
-      <c r="H79" t="s">
-        <v>108</v>
-      </c>
-      <c r="J79" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K79" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2773,13 +2800,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>178</v>
+        <v>132</v>
+      </c>
+      <c r="C80" t="s">
+        <v>125</v>
+      </c>
+      <c r="D80" t="s">
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>22</v>
-      </c>
-      <c r="J80">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K80" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2787,16 +2820,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K81" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,13 +2840,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>147</v>
+        <v>125</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K82" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2818,16 +2860,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D83" t="s">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="F83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2835,13 +2877,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2849,19 +2891,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="D85" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="F85" t="s">
-        <v>54</v>
-      </c>
-      <c r="K85" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2869,19 +2908,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="C86" t="s">
-        <v>185</v>
-      </c>
-      <c r="D86" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F86" t="s">
-        <v>54</v>
-      </c>
-      <c r="K86" t="s">
-        <v>158</v>
+        <v>21</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2889,19 +2925,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="C87" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="F87" t="s">
-        <v>54</v>
-      </c>
-      <c r="K87" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,19 +2942,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
-        <v>185</v>
-      </c>
-      <c r="D88" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="F88" t="s">
-        <v>54</v>
-      </c>
-      <c r="K88" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2929,19 +2956,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" t="s">
-        <v>185</v>
-      </c>
-      <c r="D89" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F89" t="s">
-        <v>54</v>
-      </c>
-      <c r="K89" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2949,19 +2970,25 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="D90" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="F90" t="s">
-        <v>54</v>
-      </c>
-      <c r="K90" t="s">
-        <v>193</v>
+        <v>63</v>
+      </c>
+      <c r="G90" t="s">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s">
+        <v>81</v>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2969,16 +2996,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
-      </c>
-      <c r="C91" t="s">
-        <v>185</v>
-      </c>
-      <c r="D91" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="F91" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2986,13 +3010,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s">
-        <v>185</v>
+        <v>120</v>
+      </c>
+      <c r="D92" t="s">
+        <v>153</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3000,16 +3027,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C93" t="s">
-        <v>185</v>
-      </c>
-      <c r="D93" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3017,13 +3041,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="C94" t="s">
-        <v>198</v>
+        <v>120</v>
+      </c>
+      <c r="D94" t="s">
+        <v>156</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3031,16 +3058,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>198</v>
-      </c>
-      <c r="D95" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3048,13 +3072,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="C96" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="D96" t="s">
+        <v>127</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K96" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3062,13 +3092,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>202</v>
+        <v>160</v>
+      </c>
+      <c r="C97" t="s">
+        <v>158</v>
+      </c>
+      <c r="D97" t="s">
+        <v>130</v>
       </c>
       <c r="F97" t="s">
-        <v>22</v>
-      </c>
-      <c r="J97">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K97" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3076,25 +3112,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="C98" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="F98" t="s">
-        <v>86</v>
-      </c>
-      <c r="G98" t="s">
-        <v>107</v>
-      </c>
-      <c r="H98" t="s">
-        <v>108</v>
-      </c>
-      <c r="J98" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K98" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3102,13 +3132,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>204</v>
+        <v>162</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" t="s">
+        <v>136</v>
       </c>
       <c r="F99" t="s">
-        <v>22</v>
-      </c>
-      <c r="J99">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K99" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3116,16 +3152,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="C100" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="F100" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K100" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -3133,13 +3172,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="C101" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="D101" t="s">
+        <v>165</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="K101" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3147,16 +3192,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="F102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -3164,13 +3209,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="C103" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -3178,19 +3223,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C104" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="F104" t="s">
-        <v>54</v>
-      </c>
-      <c r="K104" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -3198,19 +3240,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>185</v>
-      </c>
-      <c r="D105" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F105" t="s">
-        <v>54</v>
-      </c>
-      <c r="K105" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3218,19 +3254,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D106" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F106" t="s">
-        <v>54</v>
-      </c>
-      <c r="K106" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3238,19 +3271,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="C107" t="s">
-        <v>185</v>
-      </c>
-      <c r="D107" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="F107" t="s">
-        <v>54</v>
-      </c>
-      <c r="K107" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -3258,19 +3285,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
-      </c>
-      <c r="C108" t="s">
-        <v>185</v>
-      </c>
-      <c r="D108" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F108" t="s">
-        <v>54</v>
-      </c>
-      <c r="K108" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -3278,19 +3299,25 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="C109" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="D109" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
-      </c>
-      <c r="K109" t="s">
-        <v>193</v>
+        <v>63</v>
+      </c>
+      <c r="G109" t="s">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s">
+        <v>81</v>
+      </c>
+      <c r="J109" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -3298,16 +3325,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>216</v>
-      </c>
-      <c r="C110" t="s">
-        <v>185</v>
-      </c>
-      <c r="D110" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -3315,13 +3339,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="C111" t="s">
-        <v>185</v>
+        <v>120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>153</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,291 +3356,297 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
-      </c>
-      <c r="D112" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="C113" t="s">
-        <v>198</v>
+        <v>120</v>
+      </c>
+      <c r="D113" t="s">
+        <v>181</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>198</v>
-      </c>
-      <c r="D114" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="F114" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="C115" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="D115" t="s">
+        <v>127</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K115" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>184</v>
+      </c>
+      <c r="C116" t="s">
+        <v>158</v>
+      </c>
+      <c r="D116" t="s">
+        <v>130</v>
       </c>
       <c r="F116" t="s">
-        <v>22</v>
-      </c>
-      <c r="J116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K116" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D117" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="F117" t="s">
-        <v>86</v>
-      </c>
-      <c r="G117" t="s">
-        <v>107</v>
-      </c>
-      <c r="H117" t="s">
-        <v>108</v>
-      </c>
-      <c r="J117" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K117" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>224</v>
+        <v>186</v>
+      </c>
+      <c r="C118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D118" t="s">
+        <v>136</v>
       </c>
       <c r="F118" t="s">
-        <v>22</v>
-      </c>
-      <c r="J118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K118" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="C119" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D119" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="F119" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K119" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="C120" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="D120" t="s">
+        <v>165</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="C123" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F123" t="s">
-        <v>86</v>
-      </c>
-      <c r="G123" t="s">
-        <v>107</v>
-      </c>
-      <c r="H123" t="s">
-        <v>108</v>
-      </c>
-      <c r="J123" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>230</v>
+        <v>192</v>
+      </c>
+      <c r="C124" t="s">
+        <v>171</v>
       </c>
       <c r="F124" t="s">
-        <v>22</v>
-      </c>
-      <c r="J124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="C125" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="D125" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F125" t="s">
-        <v>86</v>
-      </c>
-      <c r="G125" t="s">
-        <v>107</v>
-      </c>
-      <c r="H125" t="s">
-        <v>108</v>
-      </c>
-      <c r="J125" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>232</v>
+        <v>194</v>
+      </c>
+      <c r="C126" t="s">
+        <v>120</v>
       </c>
       <c r="F126" t="s">
-        <v>22</v>
-      </c>
-      <c r="J126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>233</v>
-      </c>
-      <c r="C127" t="s">
-        <v>147</v>
-      </c>
-      <c r="D127" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F127" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C128" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="D128" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="F128" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="G128" t="s">
+        <v>80</v>
+      </c>
+      <c r="H128" t="s">
+        <v>81</v>
+      </c>
+      <c r="J128" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -3621,13 +3654,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>236</v>
-      </c>
-      <c r="C129" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -3635,19 +3668,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C130" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="D130" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="F130" t="s">
-        <v>54</v>
-      </c>
-      <c r="K130" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3655,19 +3685,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="C131" t="s">
-        <v>237</v>
-      </c>
-      <c r="D131" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="F131" t="s">
-        <v>54</v>
-      </c>
-      <c r="K131" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -3675,19 +3699,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C132" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="D132" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>54</v>
-      </c>
-      <c r="K132" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -3695,16 +3716,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C133" t="s">
-        <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="F133" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -3712,13 +3730,25 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="C134" t="s">
-        <v>237</v>
+        <v>120</v>
+      </c>
+      <c r="D134" t="s">
+        <v>63</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="G134" t="s">
+        <v>80</v>
+      </c>
+      <c r="H134" t="s">
+        <v>81</v>
+      </c>
+      <c r="J134" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -3726,16 +3756,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>244</v>
-      </c>
-      <c r="C135" t="s">
-        <v>237</v>
-      </c>
-      <c r="D135" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -3743,13 +3770,25 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="C136" t="s">
-        <v>237</v>
+        <v>120</v>
+      </c>
+      <c r="D136" t="s">
+        <v>150</v>
       </c>
       <c r="F136" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="G136" t="s">
+        <v>80</v>
+      </c>
+      <c r="H136" t="s">
+        <v>81</v>
+      </c>
+      <c r="J136" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -3757,19 +3796,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>247</v>
-      </c>
-      <c r="C137" t="s">
-        <v>237</v>
-      </c>
-      <c r="D137" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F137" t="s">
-        <v>54</v>
-      </c>
-      <c r="K137" t="s">
-        <v>193</v>
+        <v>21</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -3777,16 +3810,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="C138" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="F138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -3794,13 +3827,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="C139" t="s">
-        <v>147</v>
+        <v>120</v>
+      </c>
+      <c r="D139" t="s">
+        <v>208</v>
       </c>
       <c r="F139" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -3808,13 +3844,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>250</v>
+        <v>209</v>
+      </c>
+      <c r="C140" t="s">
+        <v>210</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
-      </c>
-      <c r="J140">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -3822,25 +3858,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="C141" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="D141" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="F141" t="s">
-        <v>86</v>
-      </c>
-      <c r="G141" t="s">
-        <v>107</v>
-      </c>
-      <c r="H141" t="s">
-        <v>108</v>
-      </c>
-      <c r="J141" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K141" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -3848,13 +3878,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>252</v>
+        <v>212</v>
+      </c>
+      <c r="C142" t="s">
+        <v>210</v>
+      </c>
+      <c r="D142" t="s">
+        <v>130</v>
       </c>
       <c r="F142" t="s">
-        <v>22</v>
-      </c>
-      <c r="J142">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="K142" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -3862,16 +3898,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C143" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="D143" t="s">
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="K143" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -3879,16 +3918,200 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="C144" t="s">
+        <v>210</v>
+      </c>
+      <c r="D144" t="s">
+        <v>215</v>
+      </c>
+      <c r="F144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>216</v>
+      </c>
+      <c r="C145" t="s">
+        <v>210</v>
+      </c>
+      <c r="F145" t="s">
         <v>19</v>
       </c>
-      <c r="D144" t="s">
-        <v>256</v>
-      </c>
-      <c r="F144" t="s">
-        <v>25</v>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>217</v>
+      </c>
+      <c r="C146" t="s">
+        <v>210</v>
+      </c>
+      <c r="D146" t="s">
+        <v>218</v>
+      </c>
+      <c r="F146" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>219</v>
+      </c>
+      <c r="C147" t="s">
+        <v>210</v>
+      </c>
+      <c r="F147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>220</v>
+      </c>
+      <c r="C148" t="s">
+        <v>210</v>
+      </c>
+      <c r="D148" t="s">
+        <v>165</v>
+      </c>
+      <c r="F148" t="s">
+        <v>37</v>
+      </c>
+      <c r="K148" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>221</v>
+      </c>
+      <c r="C149" t="s">
+        <v>210</v>
+      </c>
+      <c r="D149" t="s">
+        <v>105</v>
+      </c>
+      <c r="F149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>222</v>
+      </c>
+      <c r="C150" t="s">
+        <v>120</v>
+      </c>
+      <c r="F150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>223</v>
+      </c>
+      <c r="F151" t="s">
+        <v>21</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>224</v>
+      </c>
+      <c r="C152" t="s">
+        <v>120</v>
+      </c>
+      <c r="D152" t="s">
+        <v>150</v>
+      </c>
+      <c r="F152" t="s">
+        <v>63</v>
+      </c>
+      <c r="G152" t="s">
+        <v>80</v>
+      </c>
+      <c r="H152" t="s">
+        <v>81</v>
+      </c>
+      <c r="J152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>225</v>
+      </c>
+      <c r="F153" t="s">
+        <v>21</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>226</v>
+      </c>
+      <c r="C154" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" t="s">
+        <v>227</v>
+      </c>
+      <c r="F154" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>228</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" t="s">
+        <v>229</v>
+      </c>
+      <c r="F155" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3921,102 +4144,102 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="E2" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="G2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="H2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="J2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="K2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="L2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="M2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="N2" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="O2" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="P2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -4035,71 +4258,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="B9" s="3">
         <v>142</v>
@@ -4107,7 +4330,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B10" s="3">
         <v>21</v>
@@ -4115,7 +4338,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3">
         <v>52</v>
@@ -4123,15 +4346,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -4139,7 +4362,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -4147,31 +4370,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="B18" s="3">
         <v>8</v>
@@ -4179,18 +4402,18 @@
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -4210,68 +4433,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="C3" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="C5" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F619008C-7E7F-4849-AEE5-4BB39C0E1995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC63FD7-5FD1-47B1-9144-DE206B6FD8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
   </bookViews>
@@ -1812,7 +1812,7 @@
         <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1996,7 +1996,7 @@
         <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>66</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Contacts/LSTP_Contacts_WF001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Contacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC63FD7-5FD1-47B1-9144-DE206B6FD8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BE970-1480-4C8B-B96A-8EC28F54E959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5284D91C-9639-4EBE-966B-9C47A549D334}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="326">
   <si>
     <t>StepNo</t>
   </si>
@@ -149,18 +149,12 @@
     <t>CITY</t>
   </si>
   <si>
-    <t>cmb_Country</t>
-  </si>
-  <si>
     <t>selectComboBox</t>
   </si>
   <si>
     <t>COUNTRY</t>
   </si>
   <si>
-    <t>Click Next to proceed to the second section of the registration roadmap</t>
-  </si>
-  <si>
     <t>btn_Next</t>
   </si>
   <si>
@@ -947,9 +941,6 @@
     <t>Click Find to search</t>
   </si>
   <si>
-    <t>Select patient country of registration</t>
-  </si>
-  <si>
     <t>txt_Forename</t>
   </si>
   <si>
@@ -965,36 +956,6 @@
     <t>launchRegistration</t>
   </si>
   <si>
-    <t>Enter City (mandatory)</t>
-  </si>
-  <si>
-    <t>txt_City</t>
-  </si>
-  <si>
-    <t>Solihull</t>
-  </si>
-  <si>
-    <t>Dismiss validate-address dialog (Ok = save anyway)</t>
-  </si>
-  <si>
-    <t>btn_OK</t>
-  </si>
-  <si>
-    <t>Wait for address validation</t>
-  </si>
-  <si>
-    <t>Click Next to advance to Add social information</t>
-  </si>
-  <si>
-    <t>Cancel the address finder dialog</t>
-  </si>
-  <si>
-    <t>btn_AddrCancel</t>
-  </si>
-  <si>
-    <t>Wait after cancelling address finder</t>
-  </si>
-  <si>
     <t>White - British</t>
   </si>
   <si>
@@ -1035,6 +996,27 @@
   </si>
   <si>
     <t>Dismiss PDS Trace timeout - click No to decouple and open EPR</t>
+  </si>
+  <si>
+    <t>Wait after cancelling the address finder</t>
+  </si>
+  <si>
+    <t>Click Next to advance to the Add social information section</t>
+  </si>
+  <si>
+    <t>Wait for the registration form to process the Next action</t>
+  </si>
+  <si>
+    <t>Wait for the Add social information section to load</t>
+  </si>
+  <si>
+    <t>Skip address entry (address optional; PAF empty in this environment)</t>
+  </si>
+  <si>
+    <t>Wait for the Next action to process</t>
+  </si>
+  <si>
+    <t>Short wait before demographics</t>
   </si>
 </sst>
 </file>
@@ -1573,13 +1555,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -1604,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1624,19 +1606,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1644,19 +1626,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1664,13 +1646,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -1681,19 +1663,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1701,7 +1683,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -1718,7 +1700,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -1735,10 +1717,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K17" t="s">
         <v>34</v>
@@ -1749,7 +1731,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -1763,19 +1745,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>308</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" t="s">
-        <v>310</v>
+        <v>21</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1783,19 +1759,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" t="s">
         <v>37</v>
-      </c>
-      <c r="K20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1803,16 +1779,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" t="s">
-        <v>40</v>
+        <v>324</v>
       </c>
       <c r="F21" t="s">
-        <v>307</v>
+        <v>21</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1820,16 +1793,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" t="s">
-        <v>312</v>
-      </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1837,16 +1807,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
-      <c r="D23" t="s">
-        <v>316</v>
-      </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1854,13 +1821,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1868,13 +1835,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
+        <v>321</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1882,16 +1849,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="D26" t="s">
-        <v>40</v>
-      </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1899,7 +1863,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -1913,7 +1877,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
@@ -1927,19 +1891,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1947,19 +1911,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1967,19 +1931,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1987,16 +1951,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2004,10 +1968,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -2018,13 +1982,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" t="s">
         <v>171</v>
-      </c>
-      <c r="D34" t="s">
-        <v>173</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -2035,10 +1999,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -2049,13 +2013,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="F36" t="s">
         <v>24</v>
@@ -2066,10 +2030,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -2080,19 +2044,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>307</v>
+      </c>
+      <c r="F38" t="s">
+        <v>58</v>
+      </c>
+      <c r="J38" t="s">
         <v>59</v>
-      </c>
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" t="s">
-        <v>320</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-      <c r="J38" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2100,22 +2064,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>307</v>
+      </c>
+      <c r="F39" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" t="s">
         <v>62</v>
       </c>
-      <c r="C39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" t="s">
-        <v>320</v>
-      </c>
-      <c r="F39" t="s">
-        <v>63</v>
-      </c>
-      <c r="G39" t="s">
-        <v>64</v>
-      </c>
       <c r="H39" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2123,16 +2087,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2140,13 +2104,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="F41" t="s">
         <v>24</v>
@@ -2157,7 +2121,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
@@ -2171,7 +2135,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -2185,13 +2149,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F44" t="s">
         <v>24</v>
@@ -2202,10 +2166,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
@@ -2216,10 +2180,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -2236,19 +2200,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" t="s">
+        <v>312</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" t="s">
         <v>293</v>
-      </c>
-      <c r="C47" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" t="s">
-        <v>325</v>
-      </c>
-      <c r="F47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J47" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2256,10 +2220,10 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
@@ -2270,19 +2234,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
       </c>
       <c r="J49" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2290,19 +2254,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D50" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F50" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="J50" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2310,10 +2274,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F51" t="s">
         <v>19</v>
@@ -2324,13 +2288,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
         <v>24</v>
@@ -2341,13 +2305,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="F53" t="s">
         <v>24</v>
@@ -2358,10 +2322,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -2372,22 +2336,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" t="s">
         <v>78</v>
       </c>
-      <c r="C55" t="s">
-        <v>77</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="H55" t="s">
         <v>79</v>
-      </c>
-      <c r="F55" t="s">
-        <v>63</v>
-      </c>
-      <c r="G55" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" t="s">
-        <v>81</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
@@ -2398,19 +2362,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
         <v>77</v>
       </c>
-      <c r="D56" t="s">
-        <v>79</v>
-      </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2418,7 +2382,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
@@ -2432,13 +2396,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F58" t="s">
         <v>24</v>
@@ -2449,10 +2413,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -2463,13 +2427,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
         <v>24</v>
@@ -2480,10 +2444,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>
@@ -2494,19 +2458,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" t="s">
+        <v>36</v>
+      </c>
+      <c r="K62" t="s">
         <v>92</v>
-      </c>
-      <c r="C62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D62" t="s">
-        <v>93</v>
-      </c>
-      <c r="F62" t="s">
-        <v>37</v>
-      </c>
-      <c r="K62" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2514,19 +2478,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" t="s">
+        <v>36</v>
+      </c>
+      <c r="K63" t="s">
         <v>95</v>
-      </c>
-      <c r="C63" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63" t="s">
-        <v>96</v>
-      </c>
-      <c r="F63" t="s">
-        <v>37</v>
-      </c>
-      <c r="K63" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2534,19 +2498,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64" t="s">
         <v>98</v>
-      </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" t="s">
-        <v>99</v>
-      </c>
-      <c r="F64" t="s">
-        <v>37</v>
-      </c>
-      <c r="K64" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2554,19 +2518,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" t="s">
+        <v>89</v>
+      </c>
+      <c r="D65" t="s">
+        <v>100</v>
+      </c>
+      <c r="F65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65" t="s">
         <v>101</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" t="s">
-        <v>102</v>
-      </c>
-      <c r="F65" t="s">
-        <v>37</v>
-      </c>
-      <c r="K65" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2574,13 +2538,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F66" t="s">
         <v>24</v>
@@ -2591,10 +2555,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F67" t="s">
         <v>19</v>
@@ -2605,13 +2569,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" t="s">
         <v>107</v>
-      </c>
-      <c r="D68" t="s">
-        <v>109</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
@@ -2622,10 +2586,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -2636,7 +2600,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F70" t="s">
         <v>21</v>
@@ -2650,13 +2614,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" t="s">
         <v>112</v>
-      </c>
-      <c r="C71" t="s">
-        <v>113</v>
-      </c>
-      <c r="D71" t="s">
-        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>24</v>
@@ -2667,10 +2631,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F72" t="s">
         <v>19</v>
@@ -2681,16 +2645,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" t="s">
+        <v>115</v>
+      </c>
+      <c r="E73" t="s">
         <v>116</v>
-      </c>
-      <c r="C73" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" t="s">
-        <v>117</v>
-      </c>
-      <c r="E73" t="s">
-        <v>118</v>
       </c>
       <c r="F73" t="s">
         <v>24</v>
@@ -2701,10 +2665,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
@@ -2715,7 +2679,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F75" t="s">
         <v>21</v>
@@ -2729,13 +2693,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D76" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F76" t="s">
         <v>24</v>
@@ -2746,10 +2710,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F77" t="s">
         <v>19</v>
@@ -2760,19 +2724,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" t="s">
+        <v>123</v>
+      </c>
+      <c r="D78" t="s">
+        <v>125</v>
+      </c>
+      <c r="F78" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78" t="s">
         <v>126</v>
-      </c>
-      <c r="C78" t="s">
-        <v>125</v>
-      </c>
-      <c r="D78" t="s">
-        <v>127</v>
-      </c>
-      <c r="F78" t="s">
-        <v>37</v>
-      </c>
-      <c r="K78" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2780,19 +2744,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s">
+        <v>123</v>
+      </c>
+      <c r="D79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79" t="s">
         <v>129</v>
-      </c>
-      <c r="C79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D79" t="s">
-        <v>130</v>
-      </c>
-      <c r="F79" t="s">
-        <v>37</v>
-      </c>
-      <c r="K79" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2800,19 +2764,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" t="s">
+        <v>123</v>
+      </c>
+      <c r="D80" t="s">
+        <v>131</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="K80" t="s">
         <v>132</v>
-      </c>
-      <c r="C80" t="s">
-        <v>125</v>
-      </c>
-      <c r="D80" t="s">
-        <v>133</v>
-      </c>
-      <c r="F80" t="s">
-        <v>37</v>
-      </c>
-      <c r="K80" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2820,19 +2784,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" t="s">
+        <v>123</v>
+      </c>
+      <c r="D81" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81" t="s">
         <v>135</v>
-      </c>
-      <c r="C81" t="s">
-        <v>125</v>
-      </c>
-      <c r="D81" t="s">
-        <v>136</v>
-      </c>
-      <c r="F81" t="s">
-        <v>37</v>
-      </c>
-      <c r="K81" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2840,19 +2804,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" t="s">
+        <v>123</v>
+      </c>
+      <c r="D82" t="s">
+        <v>137</v>
+      </c>
+      <c r="F82" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82" t="s">
         <v>138</v>
-      </c>
-      <c r="C82" t="s">
-        <v>125</v>
-      </c>
-      <c r="D82" t="s">
-        <v>139</v>
-      </c>
-      <c r="F82" t="s">
-        <v>37</v>
-      </c>
-      <c r="K82" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2860,13 +2824,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
         <v>24</v>
@@ -2877,10 +2841,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
@@ -2891,13 +2855,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
@@ -2908,10 +2872,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F86" t="s">
         <v>21</v>
@@ -2925,13 +2889,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F87" t="s">
         <v>24</v>
@@ -2942,10 +2906,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C88" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -2956,7 +2920,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F89" t="s">
         <v>21</v>
@@ -2970,22 +2934,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F90" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
@@ -2996,7 +2960,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F91" t="s">
         <v>21</v>
@@ -3010,13 +2974,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D92" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F92" t="s">
         <v>24</v>
@@ -3027,10 +2991,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C93" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3041,13 +3005,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F94" t="s">
         <v>24</v>
@@ -3058,10 +3022,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C95" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3072,19 +3036,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D96" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K96" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3092,19 +3056,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C97" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K97" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3112,19 +3076,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K98" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3132,19 +3096,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K99" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3152,19 +3116,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K100" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -3172,19 +3136,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>156</v>
+      </c>
+      <c r="D101" t="s">
+        <v>163</v>
+      </c>
+      <c r="F101" t="s">
+        <v>36</v>
+      </c>
+      <c r="K101" t="s">
         <v>164</v>
-      </c>
-      <c r="C101" t="s">
-        <v>158</v>
-      </c>
-      <c r="D101" t="s">
-        <v>165</v>
-      </c>
-      <c r="F101" t="s">
-        <v>37</v>
-      </c>
-      <c r="K101" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3192,13 +3156,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F102" t="s">
         <v>24</v>
@@ -3209,10 +3173,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F103" t="s">
         <v>19</v>
@@ -3223,13 +3187,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F104" t="s">
         <v>24</v>
@@ -3240,10 +3204,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C105" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F105" t="s">
         <v>19</v>
@@ -3254,13 +3218,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C106" t="s">
+        <v>169</v>
+      </c>
+      <c r="D106" t="s">
         <v>171</v>
-      </c>
-      <c r="D106" t="s">
-        <v>173</v>
       </c>
       <c r="F106" t="s">
         <v>24</v>
@@ -3271,10 +3235,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C107" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F107" t="s">
         <v>19</v>
@@ -3285,7 +3249,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
@@ -3299,22 +3263,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C109" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D109" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F109" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G109" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
@@ -3325,7 +3289,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
@@ -3339,13 +3303,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C111" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F111" t="s">
         <v>24</v>
@@ -3356,10 +3320,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F112" t="s">
         <v>19</v>
@@ -3370,13 +3334,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C113" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -3387,10 +3351,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C114" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F114" t="s">
         <v>19</v>
@@ -3401,19 +3365,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C115" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D115" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K115" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -3421,19 +3385,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F116" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K116" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -3441,19 +3405,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C117" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D117" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K117" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -3461,19 +3425,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C118" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K118" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3481,19 +3445,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C119" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K119" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -3501,19 +3465,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D120" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K120" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -3521,13 +3485,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C121" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F121" t="s">
         <v>24</v>
@@ -3538,10 +3502,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C122" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3552,13 +3516,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D123" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F123" t="s">
         <v>24</v>
@@ -3569,10 +3533,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C124" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -3583,13 +3547,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C125" t="s">
+        <v>169</v>
+      </c>
+      <c r="D125" t="s">
         <v>171</v>
-      </c>
-      <c r="D125" t="s">
-        <v>173</v>
       </c>
       <c r="F125" t="s">
         <v>24</v>
@@ -3600,10 +3564,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
@@ -3614,7 +3578,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F127" t="s">
         <v>21</v>
@@ -3628,22 +3592,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D128" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F128" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G128" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H128" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
@@ -3654,7 +3618,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F129" t="s">
         <v>21</v>
@@ -3668,10 +3632,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C130" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D130" t="s">
         <v>24</v>
@@ -3685,10 +3649,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C131" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F131" t="s">
         <v>19</v>
@@ -3699,10 +3663,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C132" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D132" t="s">
         <v>24</v>
@@ -3716,10 +3680,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C133" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F133" t="s">
         <v>19</v>
@@ -3730,22 +3694,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G134" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H134" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
@@ -3756,7 +3720,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F135" t="s">
         <v>21</v>
@@ -3770,22 +3734,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C136" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D136" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F136" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G136" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H136" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
@@ -3796,7 +3760,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F137" t="s">
         <v>21</v>
@@ -3810,13 +3774,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D138" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F138" t="s">
         <v>24</v>
@@ -3827,13 +3791,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C139" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D139" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F139" t="s">
         <v>24</v>
@@ -3844,10 +3808,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C140" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F140" t="s">
         <v>19</v>
@@ -3858,19 +3822,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C141" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D141" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K141" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -3878,19 +3842,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C142" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D142" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K142" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -3898,19 +3862,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C143" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D143" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K143" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -3918,13 +3882,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C144" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D144" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F144" t="s">
         <v>24</v>
@@ -3935,10 +3899,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C145" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F145" t="s">
         <v>19</v>
@@ -3949,13 +3913,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C146" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D146" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F146" t="s">
         <v>24</v>
@@ -3966,10 +3930,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C147" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F147" t="s">
         <v>19</v>
@@ -3980,19 +3944,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C148" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D148" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K148" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -4000,13 +3964,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C149" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D149" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F149" t="s">
         <v>24</v>
@@ -4017,10 +3981,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C150" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F150" t="s">
         <v>19</v>
@@ -4031,7 +3995,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F151" t="s">
         <v>21</v>
@@ -4045,22 +4009,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C152" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D152" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F152" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G152" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H152" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J152" t="b">
         <v>1</v>
@@ -4071,7 +4035,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F153" t="s">
         <v>21</v>
@@ -4085,13 +4049,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C154" t="s">
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F154" t="s">
         <v>24</v>
@@ -4102,13 +4066,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C155" t="s">
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F155" t="s">
         <v>24</v>
@@ -4150,96 +4114,96 @@
         <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
         <v>230</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" t="s">
         <v>231</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" t="s">
         <v>232</v>
       </c>
-      <c r="D2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>233</v>
       </c>
-      <c r="F2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>234</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>235</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>236</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>237</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>238</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>239</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>240</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>241</v>
-      </c>
-      <c r="O2" t="s">
-        <v>242</v>
-      </c>
-      <c r="P2" t="s">
-        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -4258,71 +4222,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B9" s="3">
         <v>142</v>
@@ -4330,7 +4294,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B10" s="3">
         <v>21</v>
@@ -4338,7 +4302,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B11" s="3">
         <v>52</v>
@@ -4346,15 +4310,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -4362,7 +4326,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -4370,31 +4334,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B18" s="3">
         <v>8</v>
@@ -4402,18 +4366,18 @@
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -4433,13 +4397,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4447,54 +4411,54 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" t="s">
         <v>285</v>
-      </c>
-      <c r="B5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
